--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4122" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4122" uniqueCount="624">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1550,6 +1550,9 @@
   </si>
   <si>
     <t>Resources that would commonly referenced at Encounter.indication would be Condition and/or Procedure. These most closely align with DG1/PRB and PR1 respectively.</t>
+  </si>
+  <si>
+    <t>452: reference from V POV - PROBLEM LIST ENTRY (#9000010.07-.16)</t>
   </si>
   <si>
     <t>Encounter.diagnosis.use</t>
@@ -1846,7 +1849,7 @@
     <t>PV1-3 / PV1-6 / PV1-11 / PV1-42 / PV1-43</t>
   </si>
   <si>
-    <t>459: source value from VISIT - HOSPITAL LOCATION (#9000010-.22) case location</t>
+    <t>459: reference from VISIT - HOSPITAL LOCATION (#9000010-.22) case location</t>
   </si>
   <si>
     <t>Encounter.location.status</t>
@@ -12029,7 +12032,7 @@
         <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>82</v>
@@ -12124,7 +12127,7 @@
         <v>495</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>82</v>
@@ -12132,10 +12135,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12161,10 +12164,10 @@
         <v>178</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12194,10 +12197,10 @@
         <v>114</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12215,7 +12218,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12250,10 +12253,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12276,13 +12279,13 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12333,7 +12336,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12351,7 +12354,7 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
@@ -12368,10 +12371,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12394,16 +12397,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12453,7 +12456,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12471,7 +12474,7 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
@@ -12488,10 +12491,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12517,13 +12520,13 @@
         <v>235</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12573,7 +12576,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12591,7 +12594,7 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>82</v>
@@ -12608,10 +12611,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12726,10 +12729,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12846,10 +12849,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12968,10 +12971,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12997,10 +13000,10 @@
         <v>148</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13051,7 +13054,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13075,7 +13078,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13086,10 +13089,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13112,13 +13115,13 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13169,7 +13172,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13187,7 +13190,7 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>82</v>
@@ -13204,10 +13207,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13233,10 +13236,10 @@
         <v>178</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13266,10 +13269,10 @@
         <v>114</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13287,7 +13290,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13305,13 +13308,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13322,10 +13325,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13351,10 +13354,10 @@
         <v>178</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13384,10 +13387,10 @@
         <v>284</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13405,7 +13408,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13429,7 +13432,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13440,10 +13443,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13469,16 +13472,16 @@
         <v>178</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13506,10 +13509,10 @@
         <v>284</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13527,7 +13530,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13545,13 +13548,13 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13562,10 +13565,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13591,10 +13594,10 @@
         <v>178</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13624,10 +13627,10 @@
         <v>114</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13645,7 +13648,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13663,13 +13666,13 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13680,10 +13683,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13709,10 +13712,10 @@
         <v>178</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13742,10 +13745,10 @@
         <v>114</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13763,7 +13766,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13781,13 +13784,13 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13798,10 +13801,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13824,13 +13827,13 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13881,7 +13884,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13899,13 +13902,13 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -13916,10 +13919,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13945,10 +13948,10 @@
         <v>178</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13978,10 +13981,10 @@
         <v>114</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13999,7 +14002,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14017,13 +14020,13 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14034,10 +14037,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14063,13 +14066,13 @@
         <v>235</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14119,7 +14122,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14137,7 +14140,7 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>82</v>
@@ -14154,10 +14157,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14272,10 +14275,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14392,10 +14395,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14514,10 +14517,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14540,13 +14543,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14597,7 +14600,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>90</v>
@@ -14612,19 +14615,19 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>407</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>82</v>
@@ -14632,10 +14635,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14661,13 +14664,13 @@
         <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14696,10 +14699,10 @@
         <v>172</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14717,7 +14720,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14735,7 +14738,7 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>82</v>
@@ -14752,10 +14755,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14781,13 +14784,13 @@
         <v>178</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14816,10 +14819,10 @@
         <v>284</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14837,7 +14840,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14872,10 +14875,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14901,10 +14904,10 @@
         <v>208</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14955,7 +14958,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14990,10 +14993,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15016,13 +15019,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15073,7 +15076,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15091,16 +15094,16 @@
         <v>406</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>82</v>
@@ -15108,10 +15111,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15134,16 +15137,16 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15193,7 +15196,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15208,10 +15211,10 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,8 +656,7 @@
     <t>429: source value from VISIT - VISIT ID (#9000010-15001)</t>
   </si>
   <si>
-    <t>Outpat.Visit.VisitIdentifier
-Outpat.Workload.VisitIdentifier</t>
+    <t>Outpat.Visit.VisitIdentifier,Outpat.Workload.VisitIdentifier</t>
   </si>
   <si>
     <t>Encounter.identifier.period</t>
@@ -740,8 +739,7 @@
     <t>432: transform using finished on VISIT - CHECK OUT DATE&amp;TIME (#9000010-.18) case not null, &lt; now</t>
   </si>
   <si>
-    <t>Outpat.Visit.CheckOutDateTime
-Outpat.Workload.CheckOutDateTime</t>
+    <t>Outpat.Visit.CheckOutDateTime,Outpat.Workload.CheckOutDateTime</t>
   </si>
   <si>
     <t>Encounter.statusHistory</t>
@@ -1015,8 +1013,7 @@
     <t>439: source value from VISIT - SERVICE CATEGORY (#9000010-.07)</t>
   </si>
   <si>
-    <t>Outpat.Visit.ServiceCategory
-Outpat.Workload.ServiceCategory</t>
+    <t>Outpat.Visit.ServiceCategory,Outpat.Workload.ServiceCategory</t>
   </si>
   <si>
     <t>Encounter.serviceType.coding.display</t>
@@ -1368,8 +1365,7 @@
     <t>443: source value from VISIT - VISIT/ADMIT DATE&amp;TIME (#9000010-.01)</t>
   </si>
   <si>
-    <t>Outpat.Visit.VisitDateTime
-Outpat.Workload.VisitDateTime</t>
+    <t>Outpat.Visit.VisitDateTime,Outpat.Workload.VisitDateTime</t>
   </si>
   <si>
     <t>Encounter.period.end</t>
@@ -1482,8 +1478,7 @@
     <t>447: source value from V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (#9000010.07-.01 &gt; 80-.01)</t>
   </si>
   <si>
-    <t>Dim.ICD10.ICD10Code
-Dim.ICD9.ICD9Code</t>
+    <t>Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
   </si>
   <si>
     <t>Encounter.reasonCode.coding.display</t>
@@ -2304,7 +2299,7 @@
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="191.1328125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="125.1484375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="65.0078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -247,12 +253,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t xml:space="preserve">Visit
@@ -647,16 +647,16 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>429: source value from VISIT - VISIT ID (#9000010-15001)</t>
+  </si>
+  <si>
+    <t>Outpat.Visit.VisitIdentifier,Outpat.Workload.VisitIdentifier</t>
+  </si>
+  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>429: source value from VISIT - VISIT ID (#9000010-15001)</t>
-  </si>
-  <si>
-    <t>Outpat.Visit.VisitIdentifier,Outpat.Workload.VisitIdentifier</t>
   </si>
   <si>
     <t>Encounter.identifier.period</t>
@@ -724,6 +724,12 @@
     <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
   </si>
   <si>
+    <t>432: transform using finished on VISIT - CHECK OUT DATE&amp;TIME (#9000010-.18) case not null, &lt; now</t>
+  </si>
+  <si>
+    <t>Outpat.Visit.CheckOutDateTime,Outpat.Workload.CheckOutDateTime</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -734,12 +740,6 @@
   </si>
   <si>
     <t>No clear equivalent in HL7 v2; active/finished could be inferred from PV1-44, PV1-45, PV2-24; inactive could be inferred from PV2-16</t>
-  </si>
-  <si>
-    <t>432: transform using finished on VISIT - CHECK OUT DATE&amp;TIME (#9000010-.18) case not null, &lt; now</t>
-  </si>
-  <si>
-    <t>Outpat.Visit.CheckOutDateTime,Outpat.Workload.CheckOutDateTime</t>
   </si>
   <si>
     <t>Encounter.statusHistory</t>
@@ -875,6 +875,9 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-encounter-type</t>
   </si>
   <si>
+    <t>1615: source value from V CPT - CPT &gt; CPT (#9000010.18-.01 &gt; 81-)</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -884,9 +887,6 @@
     <t>PV1-4 / PV1-18</t>
   </si>
   <si>
-    <t>1615: source value from V CPT - CPT &gt; CPT (#9000010.18-.01 &gt; 81-)</t>
-  </si>
-  <si>
     <t>Encounter.serviceType</t>
   </si>
   <si>
@@ -1004,16 +1004,16 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>439: source value from VISIT - SERVICE CATEGORY (#9000010-.07)</t>
+  </si>
+  <si>
+    <t>Outpat.Visit.ServiceCategory,Outpat.Workload.ServiceCategory</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
     <t>C*E.1</t>
-  </si>
-  <si>
-    <t>439: source value from VISIT - SERVICE CATEGORY (#9000010-.07)</t>
-  </si>
-  <si>
-    <t>Outpat.Visit.ServiceCategory,Outpat.Workload.ServiceCategory</t>
   </si>
   <si>
     <t>Encounter.serviceType.coding.display</t>
@@ -1130,6 +1130,9 @@
     <t>While the encounter is always about the patient, the patient might not actually be known in all contexts of use, and there may be a group of patients that could be anonymous (such as in a group therapy for Alcoholics Anonymous - where the recording of the encounter could be used for billing on the number of people/staff and not important to the context of the specific patients) or alternately in veterinary care a herd of sheep receiving treatment (where the animals are not individually tracked).</t>
   </si>
   <si>
+    <t>440: source value from VISIT - PATIENT NAME (#9000010-.05)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1140,9 +1143,6 @@
   </si>
   <si>
     <t>PID-3</t>
-  </si>
-  <si>
-    <t>440: source value from VISIT - PATIENT NAME (#9000010-.05)</t>
   </si>
   <si>
     <t>Encounter.episodeOfCare</t>
@@ -1269,6 +1269,9 @@
     <t>Persons involved in the encounter other than the patient.</t>
   </si>
   <si>
+    <t>1614: reference from V PROVIDER - PROVIDER &gt; NEW PERSON (#9000010.06-.01 &gt; 200-)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1279,9 +1282,6 @@
   </si>
   <si>
     <t>ROL-4</t>
-  </si>
-  <si>
-    <t>1614: reference from V PROVIDER - PROVIDER &gt; NEW PERSON (#9000010.06-.01 &gt; 200-)</t>
   </si>
   <si>
     <t>Encounter.appointment</t>
@@ -1356,18 +1356,18 @@
 </t>
   </si>
   <si>
+    <t>443: source value from VISIT - VISIT/ADMIT DATE&amp;TIME (#9000010-.01)</t>
+  </si>
+  <si>
+    <t>Outpat.Visit.VisitDateTime,Outpat.Workload.VisitDateTime</t>
+  </si>
+  <si>
     <t>./low</t>
   </si>
   <si>
     <t>DR.1</t>
   </si>
   <si>
-    <t>443: source value from VISIT - VISIT/ADMIT DATE&amp;TIME (#9000010-.01)</t>
-  </si>
-  <si>
-    <t>Outpat.Visit.VisitDateTime,Outpat.Workload.VisitDateTime</t>
-  </si>
-  <si>
     <t>Encounter.period.end</t>
   </si>
   <si>
@@ -1386,13 +1386,13 @@
     <t>Period.end</t>
   </si>
   <si>
+    <t>444: source value from VISIT - CHECK OUT DATE&amp;TIME (#9000010-.18)</t>
+  </si>
+  <si>
     <t>./high</t>
   </si>
   <si>
     <t>DR.2</t>
-  </si>
-  <si>
-    <t>444: source value from VISIT - CHECK OUT DATE&amp;TIME (#9000010-.18)</t>
   </si>
   <si>
     <t>Encounter.length</t>
@@ -1538,6 +1538,9 @@
     <t>Reason the encounter takes place, as specified using information from another resource. For admissions, this is the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
   </si>
   <si>
+    <t>452: reference from V POV - PROBLEM LIST ENTRY (#9000010.07-.16)</t>
+  </si>
+  <si>
     <t>Event.reasonReference</t>
   </si>
   <si>
@@ -1545,9 +1548,6 @@
   </si>
   <si>
     <t>Resources that would commonly referenced at Encounter.indication would be Condition and/or Procedure. These most closely align with DG1/PRB and PR1 respectively.</t>
-  </si>
-  <si>
-    <t>452: reference from V POV - PROBLEM LIST ENTRY (#9000010.07-.16)</t>
   </si>
   <si>
     <t>Encounter.diagnosis.use</t>
@@ -1835,6 +1835,9 @@
     <t>The location where the encounter takes place.</t>
   </si>
   <si>
+    <t>459: reference from VISIT - HOSPITAL LOCATION (#9000010-.22) case location</t>
+  </si>
+  <si>
     <t>Event.location</t>
   </si>
   <si>
@@ -1842,9 +1845,6 @@
   </si>
   <si>
     <t>PV1-3 / PV1-6 / PV1-11 / PV1-42 / PV1-43</t>
-  </si>
-  <si>
-    <t>459: reference from VISIT - HOSPITAL LOCATION (#9000010-.22) case location</t>
   </si>
   <si>
     <t>Encounter.location.status</t>
@@ -1909,13 +1909,13 @@
     <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
   </si>
   <si>
+    <t>1599: reference from VISIT - LOC. OF ENCOUNTER &gt; LOCATION - POINTER TO INSTITUTION FILE (#4) (#9000010-.06 &gt; 9999999.06-.1)</t>
+  </si>
+  <si>
     <t>.particiaption[typeCode=PFM].role</t>
   </si>
   <si>
     <t>PL.6  &amp; PL.1</t>
-  </si>
-  <si>
-    <t>1599: reference from VISIT - LOC. OF ENCOUNTER &gt; LOCATION - POINTER TO INSTITUTION FILE (#4) (#9000010-.06 &gt; 9999999.06-.1)</t>
   </si>
   <si>
     <t>Encounter.partOf</t>
@@ -2294,12 +2294,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="191.1328125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="125.1484375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="65.0078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="125.1484375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="65.0078125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="191.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2532,16 +2532,16 @@
         <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>82</v>
@@ -3133,13 +3133,13 @@
         <v>82</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -3253,13 +3253,13 @@
         <v>82</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -3373,13 +3373,13 @@
         <v>82</v>
       </c>
       <c r="AL9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3495,13 +3495,13 @@
         <v>82</v>
       </c>
       <c r="AL10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3610,22 +3610,22 @@
         <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3731,13 +3731,13 @@
         <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3851,13 +3851,13 @@
         <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3973,19 +3973,19 @@
         <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -4095,19 +4095,19 @@
         <v>82</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -4217,19 +4217,19 @@
         <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AM16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -4334,19 +4334,19 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>206</v>
@@ -4455,19 +4455,19 @@
         <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AM18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -4575,19 +4575,19 @@
         <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -4815,13 +4815,13 @@
         <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4933,13 +4933,13 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5053,13 +5053,13 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5175,13 +5175,13 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5293,13 +5293,13 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5411,13 +5411,13 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5529,19 +5529,19 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5647,13 +5647,13 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5765,13 +5765,13 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5885,13 +5885,13 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6007,13 +6007,13 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6125,13 +6125,13 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6243,13 +6243,13 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6363,19 +6363,19 @@
         <v>277</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>279</v>
       </c>
       <c r="AO34" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -6478,22 +6478,22 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6599,13 +6599,13 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6719,13 +6719,13 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6841,19 +6841,19 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -6959,13 +6959,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7079,13 +7079,13 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7201,19 +7201,19 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AM41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -7321,19 +7321,19 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -7438,19 +7438,19 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>323</v>
@@ -7561,19 +7561,19 @@
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -7683,19 +7683,19 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -7805,19 +7805,19 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7923,19 +7923,19 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8043,19 +8043,19 @@
         <v>361</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8158,22 +8158,22 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -8276,16 +8276,16 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8394,22 +8394,22 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8515,13 +8515,13 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8635,13 +8635,13 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8757,13 +8757,13 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8874,22 +8874,22 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AM55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -8995,19 +8995,19 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AM56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -9113,19 +9113,19 @@
         <v>406</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AO57" t="s" s="2">
+      <c r="AP57" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="58" hidden="true">
@@ -9228,22 +9228,22 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -9348,22 +9348,22 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AP59" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9469,13 +9469,13 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9589,13 +9589,13 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9706,19 +9706,19 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>437</v>
@@ -9828,10 +9828,10 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>444</v>
+        <v>229</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
@@ -9840,10 +9840,10 @@
         <v>445</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="64" hidden="true">
@@ -9948,22 +9948,22 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="65" hidden="true">
@@ -10068,22 +10068,22 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AP65" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="66" hidden="true">
@@ -10189,13 +10189,13 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10309,13 +10309,13 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10431,19 +10431,19 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -10549,13 +10549,13 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10669,13 +10669,13 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10791,19 +10791,19 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AM71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="72" hidden="true">
@@ -10911,19 +10911,19 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AM72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -11028,22 +11028,22 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>320</v>
+        <v>474</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>474</v>
+        <v>323</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -11151,19 +11151,19 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AM74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="75" hidden="true">
@@ -11273,19 +11273,19 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AM75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -11395,19 +11395,19 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AM76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="77" hidden="true">
@@ -11512,22 +11512,22 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AL77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AP77" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="78" hidden="true">
@@ -11633,13 +11633,13 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11751,13 +11751,13 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11871,13 +11871,13 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11993,13 +11993,13 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12113,19 +12113,19 @@
         <v>493</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>495</v>
       </c>
       <c r="AO82" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -12231,13 +12231,13 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12349,13 +12349,13 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12469,13 +12469,13 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12589,13 +12589,13 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12707,13 +12707,13 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12827,13 +12827,13 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12949,13 +12949,13 @@
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13067,19 +13067,19 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AM90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP90" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="91" hidden="true">
@@ -13185,13 +13185,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13303,19 +13303,19 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AM92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="93" hidden="true">
@@ -13421,19 +13421,19 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="94" hidden="true">
@@ -13543,19 +13543,19 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="AM94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP94" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="95" hidden="true">
@@ -13661,19 +13661,19 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AM95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="96" hidden="true">
@@ -13779,19 +13779,19 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AM96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP96" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="97" hidden="true">
@@ -13897,19 +13897,19 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="AM97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="98" hidden="true">
@@ -14015,19 +14015,19 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="AM98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN98" t="s" s="2">
+      <c r="AO98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP98" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="99" hidden="true">
@@ -14135,13 +14135,13 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14253,13 +14253,13 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14373,13 +14373,13 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14495,13 +14495,13 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14613,19 +14613,19 @@
         <v>590</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>591</v>
       </c>
       <c r="AN103" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AO103" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AO103" t="s" s="2">
+      <c r="AP103" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="104" hidden="true">
@@ -14733,13 +14733,13 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14971,13 +14971,13 @@
         <v>82</v>
       </c>
       <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15086,22 +15086,22 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>406</v>
+        <v>614</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>615</v>
       </c>
       <c r="AO107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP107" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="108" hidden="true">
@@ -15206,16 +15206,16 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM108" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="AL108" t="s" s="2">
+      <c r="AN108" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4122" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4121" uniqueCount="627">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -806,46 +806,55 @@
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFencounterClass</t>
+  </si>
+  <si>
+    <t>614: terminologyMaps using VF_encounterClass on VISIT - PATIENT STATUS IN/OUT (#9000010-15002)</t>
+  </si>
+  <si>
+    <t>Outpat.Visit.PatientStatusInOut,Outpat.Workload.PatientStatusInOut</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>PV1-2</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory</t>
+  </si>
+  <si>
+    <t>List of past encounter classes</t>
+  </si>
+  <si>
+    <t>The class history permits the tracking of the encounters transitions without needing to go  through the resource history.  This would be used for a case where an admission starts of as an emergency encounter, then transitions into an inpatient scenario. Doing this and not restarting a new encounter ensures that any lab/diagnostic results can more easily follow the patient and not require re-processing and not get lost or cancelled during a kind of discharge from emergency to inpatient.</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.id</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.extension</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.class</t>
+  </si>
+  <si>
+    <t>inpatient | outpatient | ambulatory | emergency +</t>
+  </si>
+  <si>
+    <t>inpatient | outpatient | ambulatory | emergency +.</t>
+  </si>
+  <si>
     <t>Classification of the encounter.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>PV1-2</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory</t>
-  </si>
-  <si>
-    <t>List of past encounter classes</t>
-  </si>
-  <si>
-    <t>The class history permits the tracking of the encounters transitions without needing to go  through the resource history.  This would be used for a case where an admission starts of as an emergency encounter, then transitions into an inpatient scenario. Doing this and not restarting a new encounter ensures that any lab/diagnostic results can more easily follow the patient and not require re-processing and not get lost or cancelled during a kind of discharge from emergency to inpatient.</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.id</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.extension</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.class</t>
-  </si>
-  <si>
-    <t>inpatient | outpatient | ambulatory | emergency +</t>
-  </si>
-  <si>
-    <t>inpatient | outpatient | ambulatory | emergency +.</t>
   </si>
   <si>
     <t>Encounter.classHistory.period</t>
@@ -5487,13 +5496,11 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y27" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y27" s="2"/>
+      <c r="Z27" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5526,30 +5533,30 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5575,10 +5582,10 @@
         <v>235</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5629,7 +5636,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5664,10 +5671,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5782,10 +5789,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5902,10 +5909,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6024,10 +6031,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6053,10 +6060,10 @@
         <v>251</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6086,10 +6093,10 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -6107,7 +6114,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>90</v>
@@ -6142,10 +6149,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6171,10 +6178,10 @@
         <v>208</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6225,7 +6232,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
@@ -6260,10 +6267,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6289,13 +6296,13 @@
         <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6324,10 +6331,10 @@
         <v>183</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6345,7 +6352,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6360,30 +6367,30 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6409,10 +6416,10 @@
         <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6439,31 +6446,31 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6484,7 +6491,7 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>160</v>
@@ -6493,15 +6500,15 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6616,10 +6623,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6736,10 +6743,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6765,16 +6772,16 @@
         <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6823,7 +6830,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6847,21 +6854,21 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6976,10 +6983,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7096,10 +7103,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7125,16 +7132,16 @@
         <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7183,7 +7190,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7207,21 +7214,21 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7247,13 +7254,13 @@
         <v>156</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7303,7 +7310,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7327,21 +7334,21 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7367,14 +7374,14 @@
         <v>110</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7423,7 +7430,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7438,30 +7445,30 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7487,14 +7494,14 @@
         <v>156</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7543,7 +7550,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7567,21 +7574,21 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7604,19 +7611,19 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7665,7 +7672,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7689,21 +7696,21 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7729,16 +7736,16 @@
         <v>156</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7787,7 +7794,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7811,21 +7818,21 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7851,10 +7858,10 @@
         <v>178</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7881,31 +7888,31 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Z47" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7929,25 +7936,25 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7966,16 +7973,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8025,7 +8032,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8040,30 +8047,30 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8086,13 +8093,13 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8143,7 +8150,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8164,28 +8171,28 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>160</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8204,13 +8211,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8261,7 +8268,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8282,10 +8289,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8296,10 +8303,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8325,10 +8332,10 @@
         <v>235</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8379,7 +8386,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8400,24 +8407,24 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8532,10 +8539,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8652,10 +8659,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8774,10 +8781,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8803,13 +8810,13 @@
         <v>178</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8838,10 +8845,10 @@
         <v>183</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8859,7 +8866,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8880,24 +8887,24 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8923,10 +8930,10 @@
         <v>208</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8977,7 +8984,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9001,21 +9008,21 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9038,13 +9045,13 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9095,7 +9102,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9110,30 +9117,30 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9156,13 +9163,13 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9213,7 +9220,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9234,24 +9241,24 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9277,13 +9284,13 @@
         <v>208</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9333,7 +9340,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9354,24 +9361,24 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9486,10 +9493,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9606,10 +9613,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9632,16 +9639,16 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9691,7 +9698,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9700,36 +9707,36 @@
         <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9752,23 +9759,23 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>82</v>
@@ -9813,7 +9820,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9822,13 +9829,13 @@
         <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>229</v>
@@ -9837,21 +9844,21 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9874,16 +9881,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9933,7 +9940,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9954,28 +9961,28 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9997,13 +10004,13 @@
         <v>178</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10032,10 +10039,10 @@
         <v>114</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10053,7 +10060,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10074,24 +10081,24 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10206,10 +10213,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10326,10 +10333,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10355,16 +10362,16 @@
         <v>251</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10413,7 +10420,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10437,21 +10444,21 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10566,10 +10573,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10686,10 +10693,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10715,16 +10722,16 @@
         <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10773,7 +10780,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10797,21 +10804,21 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10837,13 +10844,13 @@
         <v>156</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10893,7 +10900,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10917,21 +10924,21 @@
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10957,14 +10964,14 @@
         <v>110</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11013,7 +11020,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11028,30 +11035,30 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11077,14 +11084,14 @@
         <v>156</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11133,7 +11140,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11157,21 +11164,21 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11194,19 +11201,19 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11255,7 +11262,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11279,21 +11286,21 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11319,16 +11326,16 @@
         <v>156</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11377,7 +11384,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11401,25 +11408,25 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11438,16 +11445,16 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11497,7 +11504,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11518,24 +11525,24 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11561,10 +11568,10 @@
         <v>235</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11615,7 +11622,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11639,7 +11646,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11650,10 +11657,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11768,10 +11775,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11888,10 +11895,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12010,14 +12017,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12036,16 +12043,16 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12095,7 +12102,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>90</v>
@@ -12110,30 +12117,30 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12159,10 +12166,10 @@
         <v>178</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12192,28 +12199,28 @@
         <v>114</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12248,10 +12255,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12274,13 +12281,13 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12331,7 +12338,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12355,7 +12362,7 @@
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12366,10 +12373,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12392,16 +12399,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12451,7 +12458,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12475,7 +12482,7 @@
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12486,10 +12493,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12515,13 +12522,13 @@
         <v>235</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12571,7 +12578,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12595,7 +12602,7 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12606,10 +12613,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12724,10 +12731,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12844,10 +12851,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12966,10 +12973,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12995,10 +13002,10 @@
         <v>148</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13049,7 +13056,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13079,15 +13086,15 @@
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13110,13 +13117,13 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13167,7 +13174,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13191,7 +13198,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13202,10 +13209,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13231,10 +13238,10 @@
         <v>178</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13264,28 +13271,28 @@
         <v>114</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13309,21 +13316,21 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13349,10 +13356,10 @@
         <v>178</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13379,31 +13386,31 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13433,15 +13440,15 @@
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13467,16 +13474,16 @@
         <v>178</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13501,13 +13508,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13525,7 +13532,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13549,21 +13556,21 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13589,10 +13596,10 @@
         <v>178</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13622,28 +13629,28 @@
         <v>114</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13667,21 +13674,21 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13707,10 +13714,10 @@
         <v>178</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13740,28 +13747,28 @@
         <v>114</v>
       </c>
       <c r="Y96" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF96" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13785,21 +13792,21 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13822,13 +13829,13 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13879,7 +13886,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13903,21 +13910,21 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13943,10 +13950,10 @@
         <v>178</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13976,28 +13983,28 @@
         <v>114</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14021,21 +14028,21 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14061,13 +14068,13 @@
         <v>235</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14117,7 +14124,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14141,7 +14148,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14152,10 +14159,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14270,10 +14277,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14390,10 +14397,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14512,10 +14519,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14538,13 +14545,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14595,7 +14602,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>90</v>
@@ -14610,30 +14617,30 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14659,13 +14666,13 @@
         <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14694,10 +14701,10 @@
         <v>172</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14715,7 +14722,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14739,7 +14746,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14750,10 +14757,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14779,13 +14786,13 @@
         <v>178</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14811,13 +14818,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14835,7 +14842,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14870,10 +14877,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14899,10 +14906,10 @@
         <v>208</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14953,7 +14960,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14977,7 +14984,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -14988,10 +14995,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15014,13 +15021,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15071,7 +15078,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15086,30 +15093,30 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15132,16 +15139,16 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15191,7 +15198,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15212,10 +15219,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -724,7 +724,7 @@
     <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
   </si>
   <si>
-    <t>432: transform using finished on VISIT - CHECK OUT DATE&amp;TIME (#9000010-.18) case not null, &lt; now</t>
+    <t>432: fixed value = #finished when VISIT - CHECK OUT DATE&amp;TIME (#9000010-.18) case not null, &lt; now</t>
   </si>
   <si>
     <t>Outpat.Visit.CheckOutDateTime,Outpat.Workload.CheckOutDateTime</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4121" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4121" uniqueCount="628">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1257,6 +1257,9 @@
   </si>
   <si>
     <t>The period of time that the specified participant participated in the encounter. These can overlap or be sub-sets of the overall encounter's period.</t>
+  </si>
+  <si>
+    <t>1799: target not supported</t>
   </si>
   <si>
     <t>.time</t>
@@ -8999,7 +9002,7 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
@@ -9008,21 +9011,21 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9045,13 +9048,13 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9102,7 +9105,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9117,30 +9120,30 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9163,13 +9166,13 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9220,7 +9223,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9244,21 +9247,21 @@
         <v>381</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9284,13 +9287,13 @@
         <v>208</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9340,7 +9343,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9361,24 +9364,24 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9493,10 +9496,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9613,10 +9616,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9639,16 +9642,16 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9698,7 +9701,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9707,36 +9710,36 @@
         <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9759,23 +9762,23 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>82</v>
@@ -9820,7 +9823,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9829,13 +9832,13 @@
         <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>229</v>
@@ -9844,21 +9847,21 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9881,16 +9884,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9940,7 +9943,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9961,28 +9964,28 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10004,13 +10007,13 @@
         <v>178</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10039,10 +10042,10 @@
         <v>114</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10060,7 +10063,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10081,24 +10084,24 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10213,10 +10216,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10333,10 +10336,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10455,10 +10458,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10573,10 +10576,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10693,10 +10696,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10815,10 +10818,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10935,10 +10938,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11035,10 +11038,10 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>82</v>
@@ -11055,10 +11058,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11175,10 +11178,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11297,10 +11300,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11419,14 +11422,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11445,16 +11448,16 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11504,7 +11507,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11525,24 +11528,24 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11568,10 +11571,10 @@
         <v>235</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11622,7 +11625,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11646,7 +11649,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11657,10 +11660,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11775,10 +11778,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11895,10 +11898,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12017,14 +12020,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12043,16 +12046,16 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12102,7 +12105,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>90</v>
@@ -12117,30 +12120,30 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12166,10 +12169,10 @@
         <v>178</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12199,10 +12202,10 @@
         <v>114</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12220,7 +12223,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12255,10 +12258,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12281,13 +12284,13 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12338,7 +12341,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12362,7 +12365,7 @@
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12373,10 +12376,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12399,16 +12402,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12458,7 +12461,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12482,7 +12485,7 @@
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12493,10 +12496,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12522,13 +12525,13 @@
         <v>235</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12578,7 +12581,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12602,7 +12605,7 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12613,10 +12616,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12731,10 +12734,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12851,10 +12854,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12973,10 +12976,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13002,10 +13005,10 @@
         <v>148</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13056,7 +13059,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13086,15 +13089,15 @@
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13117,13 +13120,13 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13174,7 +13177,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13198,7 +13201,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13209,10 +13212,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13238,10 +13241,10 @@
         <v>178</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13271,10 +13274,10 @@
         <v>114</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13292,7 +13295,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13316,21 +13319,21 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13356,10 +13359,10 @@
         <v>178</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13389,10 +13392,10 @@
         <v>287</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13410,7 +13413,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13440,15 +13443,15 @@
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13474,16 +13477,16 @@
         <v>178</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13511,10 +13514,10 @@
         <v>287</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13532,7 +13535,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13556,21 +13559,21 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13596,10 +13599,10 @@
         <v>178</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13629,10 +13632,10 @@
         <v>114</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13650,7 +13653,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13674,21 +13677,21 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13714,10 +13717,10 @@
         <v>178</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13747,10 +13750,10 @@
         <v>114</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13768,7 +13771,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13792,21 +13795,21 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13829,13 +13832,13 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13886,7 +13889,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13910,21 +13913,21 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13950,10 +13953,10 @@
         <v>178</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13983,10 +13986,10 @@
         <v>114</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14004,7 +14007,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14028,21 +14031,21 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14068,13 +14071,13 @@
         <v>235</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14124,7 +14127,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14148,7 +14151,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14159,10 +14162,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14277,10 +14280,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14397,10 +14400,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14519,10 +14522,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14545,13 +14548,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14602,7 +14605,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>90</v>
@@ -14617,30 +14620,30 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14666,13 +14669,13 @@
         <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14701,10 +14704,10 @@
         <v>172</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14722,7 +14725,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14746,7 +14749,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14757,10 +14760,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14786,13 +14789,13 @@
         <v>178</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14821,10 +14824,10 @@
         <v>287</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14842,7 +14845,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14877,10 +14880,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14906,10 +14909,10 @@
         <v>208</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14960,7 +14963,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14984,7 +14987,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -14995,10 +14998,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15021,13 +15024,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15078,7 +15081,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15093,30 +15096,30 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15139,16 +15142,16 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15198,7 +15201,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15219,10 +15222,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file VISIT (#9000010) to us-core-encounter</t>
+    <t>This StructureDefinition contains the maps for VistA file VISIT (9000010) to us-core-encounter</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -647,7 +647,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>429: source value from VISIT - VISIT ID (#9000010-15001)</t>
+    <t>429: source value from VISIT - VISIT ID (9000010-15001)</t>
   </si>
   <si>
     <t>Outpat.Visit.VisitIdentifier,Outpat.Workload.VisitIdentifier</t>
@@ -724,7 +724,7 @@
     <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
   </si>
   <si>
-    <t>432: fixed value = #finished when VISIT - CHECK OUT DATE&amp;TIME (#9000010-.18) case not null, &lt; now</t>
+    <t>432: fixed value = #finished when VISIT - CHECK OUT DATE&amp;TIME (9000010-.18) case not null, &lt; now</t>
   </si>
   <si>
     <t>Outpat.Visit.CheckOutDateTime,Outpat.Workload.CheckOutDateTime</t>
@@ -809,7 +809,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFencounterClass</t>
   </si>
   <si>
-    <t>614: terminologyMaps using VF_encounterClass on VISIT - PATIENT STATUS IN/OUT (#9000010-15002)</t>
+    <t>614: terminologyMaps using VF_encounterClass on VISIT - PATIENT STATUS IN/OUT (9000010-15002)</t>
   </si>
   <si>
     <t>Outpat.Visit.PatientStatusInOut,Outpat.Workload.PatientStatusInOut</t>
@@ -884,7 +884,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-encounter-type</t>
   </si>
   <si>
-    <t>1615: source value from V CPT - CPT &gt; CPT (#9000010.18-.01 &gt; 81-)</t>
+    <t>1615: source value from V CPT - CPT &gt; CPT (9000010.18-.01 &gt; 81-)</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1013,7 +1013,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>439: source value from VISIT - SERVICE CATEGORY (#9000010-.07)</t>
+    <t>439: source value from VISIT - SERVICE CATEGORY (9000010-.07)</t>
   </si>
   <si>
     <t>Outpat.Visit.ServiceCategory,Outpat.Workload.ServiceCategory</t>
@@ -1139,7 +1139,7 @@
     <t>While the encounter is always about the patient, the patient might not actually be known in all contexts of use, and there may be a group of patients that could be anonymous (such as in a group therapy for Alcoholics Anonymous - where the recording of the encounter could be used for billing on the number of people/staff and not important to the context of the specific patients) or alternately in veterinary care a herd of sheep receiving treatment (where the animals are not individually tracked).</t>
   </si>
   <si>
-    <t>440: source value from VISIT - PATIENT NAME (#9000010-.05)</t>
+    <t>440: reference from VISIT - PATIENT NAME (9000010-.05)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1281,7 +1281,7 @@
     <t>Persons involved in the encounter other than the patient.</t>
   </si>
   <si>
-    <t>1614: reference from V PROVIDER - PROVIDER &gt; NEW PERSON (#9000010.06-.01 &gt; 200-)</t>
+    <t>1614: reference from V PROVIDER - PROVIDER &gt; NEW PERSON (9000010.06-.01 &gt; 200-)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1368,7 +1368,7 @@
 </t>
   </si>
   <si>
-    <t>443: source value from VISIT - VISIT/ADMIT DATE&amp;TIME (#9000010-.01)</t>
+    <t>443: source value from VISIT - VISIT/ADMIT DATE&amp;TIME (9000010-.01)</t>
   </si>
   <si>
     <t>Outpat.Visit.VisitDateTime,Outpat.Workload.VisitDateTime</t>
@@ -1398,7 +1398,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>444: source value from VISIT - CHECK OUT DATE&amp;TIME (#9000010-.18)</t>
+    <t>444: source value from VISIT - CHECK OUT DATE&amp;TIME (9000010-.18)</t>
   </si>
   <si>
     <t>./high</t>
@@ -1487,7 +1487,7 @@
     <t>Encounter.reasonCode.coding.code</t>
   </si>
   <si>
-    <t>447: source value from V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (#9000010.07-.01 &gt; 80-.01)</t>
+    <t>447: source value from V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.07-.01 &gt; 80-.01)</t>
   </si>
   <si>
     <t>Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
@@ -1550,7 +1550,7 @@
     <t>Reason the encounter takes place, as specified using information from another resource. For admissions, this is the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
   </si>
   <si>
-    <t>452: reference from V POV - PROBLEM LIST ENTRY (#9000010.07-.16)</t>
+    <t>452: reference from V POV - PROBLEM LIST ENTRY (9000010.07-.16)</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1847,7 +1847,7 @@
     <t>The location where the encounter takes place.</t>
   </si>
   <si>
-    <t>459: reference from VISIT - HOSPITAL LOCATION (#9000010-.22) case location</t>
+    <t>459: reference from VISIT - HOSPITAL LOCATION (9000010-.22) case location</t>
   </si>
   <si>
     <t>Event.location</t>
@@ -1921,7 +1921,7 @@
     <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
   </si>
   <si>
-    <t>1599: reference from VISIT - LOC. OF ENCOUNTER &gt; LOCATION - POINTER TO INSTITUTION FILE (#4) (#9000010-.06 &gt; 9999999.06-.1)</t>
+    <t>1599: reference from VISIT - LOC. OF ENCOUNTER &gt; LOCATION - POINTER TO INSTITUTION FILE (#4) (9000010-.06 &gt; 9999999.06-.1)</t>
   </si>
   <si>
     <t>.particiaption[typeCode=PFM].role</t>
@@ -2306,7 +2306,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="125.1484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="123.609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="65.0078125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1921,7 +1921,7 @@
     <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
   </si>
   <si>
-    <t>1599: reference from VISIT - LOC. OF ENCOUNTER &gt; LOCATION - POINTER TO INSTITUTION FILE (#4) (9000010-.06 &gt; 9999999.06-.1)</t>
+    <t>1599: reference from VISIT - LOC. OF ENCOUNTER &gt; LOCATION - NAME (9000010-.06 &gt; 9999999.06-.01)</t>
   </si>
   <si>
     <t>.particiaption[typeCode=PFM].role</t>
@@ -2306,7 +2306,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="123.609375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="97.65625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="65.0078125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4121" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4121" uniqueCount="634">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -887,6 +887,9 @@
     <t>1615: source value from V CPT - CPT &gt; CPT (9000010.18-.01 &gt; 81-)</t>
   </si>
   <si>
+    <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -1142,6 +1145,9 @@
     <t>440: reference from VISIT - PATIENT NAME (9000010-.05)</t>
   </si>
   <si>
+    <t>Outpat.Visit.PatientIEN,Outpat.Workload.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1284,6 +1290,9 @@
     <t>1614: reference from V PROVIDER - PROVIDER &gt; NEW PERSON (9000010.06-.01 &gt; 200-)</t>
   </si>
   <si>
+    <t>Outpat.VProvider.ProviderIEN,Outpat.WorkloadVProvider.ProviderIEN</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1371,7 +1380,7 @@
     <t>443: source value from VISIT - VISIT/ADMIT DATE&amp;TIME (9000010-.01)</t>
   </si>
   <si>
-    <t>Outpat.Visit.VisitDateTime,Outpat.Workload.VisitDateTime</t>
+    <t>Immun.ImmunizationContraRefusalEvent.VisitDateTime,Outpat.Visit.VisitDateTime,Outpat.VisitLogic.VisitDateTime,Outpat.Workload.VisitDateTime</t>
   </si>
   <si>
     <t>./low</t>
@@ -1490,7 +1499,8 @@
     <t>447: source value from V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.07-.01 &gt; 80-.01)</t>
   </si>
   <si>
-    <t>Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
+    <t>Outpat.VDiagnosis.ICDIEN,Outpat.WorkloadVDiagnosis.ICDIEN
+Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
   </si>
   <si>
     <t>Encounter.reasonCode.coding.display</t>
@@ -1551,6 +1561,9 @@
   </si>
   <si>
     <t>452: reference from V POV - PROBLEM LIST ENTRY (9000010.07-.16)</t>
+  </si>
+  <si>
+    <t>Outpat.VDiagnosis.ProblemListIEN,Outpat.WorkloadVDiagnosis.ProblemListIEN</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1850,6 +1863,9 @@
     <t>459: reference from VISIT - HOSPITAL LOCATION (9000010-.22) case location</t>
   </si>
   <si>
+    <t>Outpat.Visit.LocationIEN,Outpat.Workload.LocationIEN</t>
+  </si>
+  <si>
     <t>Event.location</t>
   </si>
   <si>
@@ -1922,6 +1938,9 @@
   </si>
   <si>
     <t>1599: reference from VISIT - LOC. OF ENCOUNTER &gt; LOCATION - NAME (9000010-.06 &gt; 9999999.06-.01)</t>
+  </si>
+  <si>
+    <t>Outpat.Visit.InstitutionIEN,Outpat.Workload.InstitutionIEN</t>
   </si>
   <si>
     <t>.particiaption[typeCode=PFM].role</t>
@@ -2307,7 +2326,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="97.65625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="65.0078125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="217.51953125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -6373,27 +6392,27 @@
         <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>258</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6419,10 +6438,10 @@
         <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6449,13 +6468,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6473,7 +6492,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6494,7 +6513,7 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>160</v>
@@ -6503,15 +6522,15 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6626,10 +6645,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6746,10 +6765,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6775,16 +6794,16 @@
         <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6833,7 +6852,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6857,21 +6876,21 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6986,10 +7005,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7106,10 +7125,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7135,16 +7154,16 @@
         <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7193,7 +7212,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7217,21 +7236,21 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7257,13 +7276,13 @@
         <v>156</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7313,7 +7332,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7337,21 +7356,21 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7377,14 +7396,14 @@
         <v>110</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7433,7 +7452,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7448,30 +7467,30 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7497,14 +7516,14 @@
         <v>156</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7553,7 +7572,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7577,21 +7596,21 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7614,19 +7633,19 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7675,7 +7694,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7699,21 +7718,21 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7739,16 +7758,16 @@
         <v>156</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7797,7 +7816,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7821,21 +7840,21 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7861,10 +7880,10 @@
         <v>178</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7891,13 +7910,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7915,7 +7934,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7939,25 +7958,25 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7976,16 +7995,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8035,7 +8054,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8050,30 +8069,30 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8096,13 +8115,13 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8153,7 +8172,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8174,28 +8193,28 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>160</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8214,13 +8233,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8271,7 +8290,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8292,10 +8311,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8306,10 +8325,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8335,10 +8354,10 @@
         <v>235</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8389,7 +8408,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8410,24 +8429,24 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8542,10 +8561,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8662,10 +8681,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8784,10 +8803,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8813,13 +8832,13 @@
         <v>178</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8848,28 +8867,28 @@
         <v>183</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8890,24 +8909,24 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8933,10 +8952,10 @@
         <v>208</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8987,7 +9006,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9002,7 +9021,7 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
@@ -9011,21 +9030,21 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9048,13 +9067,13 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9105,7 +9124,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9120,30 +9139,30 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9166,13 +9185,13 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9223,7 +9242,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9244,24 +9263,24 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9287,13 +9306,13 @@
         <v>208</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9343,7 +9362,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9364,24 +9383,24 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9496,10 +9515,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9616,10 +9635,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9642,16 +9661,16 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9701,7 +9720,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9710,36 +9729,36 @@
         <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9762,23 +9781,23 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>82</v>
@@ -9823,7 +9842,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9832,13 +9851,13 @@
         <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>229</v>
@@ -9847,21 +9866,21 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9884,16 +9903,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9943,7 +9962,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9964,28 +9983,28 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10007,13 +10026,13 @@
         <v>178</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10042,10 +10061,10 @@
         <v>114</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10063,7 +10082,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10084,24 +10103,24 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10216,10 +10235,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10336,10 +10355,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10365,16 +10384,16 @@
         <v>251</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10423,7 +10442,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10447,21 +10466,21 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10576,10 +10595,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10696,10 +10715,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10725,16 +10744,16 @@
         <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10783,7 +10802,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10807,21 +10826,21 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10847,13 +10866,13 @@
         <v>156</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10903,7 +10922,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10927,21 +10946,21 @@
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10967,14 +10986,14 @@
         <v>110</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11023,7 +11042,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11038,30 +11057,30 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11087,14 +11106,14 @@
         <v>156</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11143,7 +11162,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11167,21 +11186,21 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11204,19 +11223,19 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11265,7 +11284,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11289,21 +11308,21 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11329,16 +11348,16 @@
         <v>156</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11387,7 +11406,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11411,25 +11430,25 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11448,16 +11467,16 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11507,7 +11526,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11528,24 +11547,24 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11571,10 +11590,10 @@
         <v>235</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11625,7 +11644,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11649,7 +11668,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11660,10 +11679,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11778,10 +11797,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11898,10 +11917,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12020,14 +12039,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12046,16 +12065,16 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12105,7 +12124,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>90</v>
@@ -12120,30 +12139,30 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12169,10 +12188,10 @@
         <v>178</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12202,28 +12221,28 @@
         <v>114</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="Z83" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12258,10 +12277,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12284,13 +12303,13 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12341,7 +12360,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12365,7 +12384,7 @@
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12376,10 +12395,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12402,16 +12421,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12461,7 +12480,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12485,7 +12504,7 @@
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12496,10 +12515,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12525,13 +12544,13 @@
         <v>235</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12581,7 +12600,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12605,7 +12624,7 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12616,10 +12635,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12734,10 +12753,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12854,10 +12873,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12976,10 +12995,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13005,10 +13024,10 @@
         <v>148</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13059,7 +13078,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13089,15 +13108,15 @@
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13120,13 +13139,13 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13177,7 +13196,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13201,7 +13220,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13212,10 +13231,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13241,10 +13260,10 @@
         <v>178</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13274,28 +13293,28 @@
         <v>114</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="Z92" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13319,21 +13338,21 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13359,10 +13378,10 @@
         <v>178</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13389,31 +13408,31 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="Z93" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13443,15 +13462,15 @@
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13477,16 +13496,16 @@
         <v>178</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13511,13 +13530,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13535,7 +13554,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13559,21 +13578,21 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13599,10 +13618,10 @@
         <v>178</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13632,28 +13651,28 @@
         <v>114</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="Z95" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13677,21 +13696,21 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13717,10 +13736,10 @@
         <v>178</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13750,28 +13769,28 @@
         <v>114</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="Z96" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF96" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13795,21 +13814,21 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13832,13 +13851,13 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13889,7 +13908,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13913,21 +13932,21 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13953,10 +13972,10 @@
         <v>178</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13986,28 +14005,28 @@
         <v>114</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="Z98" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14031,21 +14050,21 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14071,13 +14090,13 @@
         <v>235</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14127,7 +14146,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14151,7 +14170,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14162,10 +14181,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14280,10 +14299,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14400,10 +14419,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14522,10 +14541,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14548,13 +14567,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14605,7 +14624,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>90</v>
@@ -14620,30 +14639,30 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>82</v>
+        <v>599</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14669,13 +14688,13 @@
         <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14704,28 +14723,28 @@
         <v>172</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="Z104" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14749,7 +14768,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14760,10 +14779,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14789,13 +14808,13 @@
         <v>178</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14821,31 +14840,31 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="Z105" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14880,10 +14899,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14909,10 +14928,10 @@
         <v>208</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14963,7 +14982,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14987,7 +15006,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -14998,10 +15017,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15024,13 +15043,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15081,7 +15100,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15096,30 +15115,30 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>82</v>
+        <v>624</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15142,16 +15161,16 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15201,7 +15220,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15222,10 +15241,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$123</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4121" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4694" uniqueCount="661">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,10 +617,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/terminology/VistADefinedTerms/9000010-15001</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>429-1: fixed value = http://va.gov/terminology/VistADefinedTerms/9000010-15001</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>
@@ -899,34 +905,13 @@
     <t>PV1-4 / PV1-18</t>
   </si>
   <si>
-    <t>Encounter.serviceType</t>
-  </si>
-  <si>
-    <t>Specific type of service</t>
-  </si>
-  <si>
-    <t>Broad categorization of the service that is to be provided (e.g. cardiology).</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Broad categorization of the service that is to be provided.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
-  </si>
-  <si>
-    <t>PV1-10</t>
-  </si>
-  <si>
-    <t>Encounter.serviceType.id</t>
-  </si>
-  <si>
-    <t>Encounter.serviceType.extension</t>
-  </si>
-  <si>
-    <t>Encounter.serviceType.coding</t>
+    <t>Encounter.type.id</t>
+  </si>
+  <si>
+    <t>Encounter.type.extension</t>
+  </si>
+  <si>
+    <t>Encounter.type.coding</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -950,13 +935,13 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>Encounter.serviceType.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.serviceType.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.serviceType.coding.system</t>
+    <t>Encounter.type.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.type.coding.system</t>
   </si>
   <si>
     <t>Identity of the terminology system</t>
@@ -971,16 +956,22 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://www.ama-assn.org/go/cpt</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
+    <t>1615-1: fixed value = http://www.ama-assn.org/go/cpt</t>
+  </si>
+  <si>
     <t>./codeSystem</t>
   </si>
   <si>
     <t>C*E.3</t>
   </si>
   <si>
-    <t>Encounter.serviceType.coding.version</t>
+    <t>Encounter.type.coding.version</t>
   </si>
   <si>
     <t>Version of the system - if relevant</t>
@@ -1001,7 +992,7 @@
     <t>C*E.7</t>
   </si>
   <si>
-    <t>Encounter.serviceType.coding.code</t>
+    <t>Encounter.type.coding.code</t>
   </si>
   <si>
     <t>Symbol in syntax defined by the system</t>
@@ -1016,10 +1007,11 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>439: source value from VISIT - SERVICE CATEGORY (9000010-.07)</t>
-  </si>
-  <si>
-    <t>Outpat.Visit.ServiceCategory,Outpat.Workload.ServiceCategory</t>
+    <t>1615-2: source value from V CPT - CPT &gt; CPT - CPT CODE (9000010.18-.01 &gt; 81-.01)</t>
+  </si>
+  <si>
+    <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN
+Dim.CPT.CPTCode,Dim.CPT.CPTCode</t>
   </si>
   <si>
     <t>./code</t>
@@ -1028,7 +1020,7 @@
     <t>C*E.1</t>
   </si>
   <si>
-    <t>Encounter.serviceType.coding.display</t>
+    <t>Encounter.type.coding.display</t>
   </si>
   <si>
     <t>Representation defined by the system</t>
@@ -1043,13 +1035,20 @@
     <t>Coding.display</t>
   </si>
   <si>
+    <t>1615-3: source value from V CPT - CPT &gt; CPT - SHORT NAME (9000010.18-.01 &gt; 81-2)</t>
+  </si>
+  <si>
+    <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN
+Dim.CPT.CPTName,Dim.CPT.CPTName</t>
+  </si>
+  <si>
     <t>CV.displayName</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
   </si>
   <si>
-    <t>Encounter.serviceType.coding.userSelected</t>
+    <t>Encounter.type.coding.userSelected</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -1077,28 +1076,97 @@
     <t>Sometimes implied by being first</t>
   </si>
   <si>
+    <t>Encounter.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>1615-4: source value from V CPT - CPT &gt; CPT - SHORT NAME (9000010.18-.01 &gt; 81-2)</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType</t>
+  </si>
+  <si>
+    <t>Specific type of service</t>
+  </si>
+  <si>
+    <t>Broad categorization of the service that is to be provided (e.g. cardiology).</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Broad categorization of the service that is to be provided.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+  </si>
+  <si>
+    <t>PV1-10</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.id</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.extension</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding.system</t>
+  </si>
+  <si>
+    <t>http://va.gov/terminology/VistADefinedTerms/9000010-.07</t>
+  </si>
+  <si>
+    <t>439-1: fixed value = http://va.gov/terminology/VistADefinedTerms/9000010-.07</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding.code</t>
+  </si>
+  <si>
+    <t>439: source value from VISIT - SERVICE CATEGORY (9000010-.07)</t>
+  </si>
+  <si>
+    <t>Outpat.Visit.ServiceCategory,Outpat.Workload.ServiceCategory</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding.userSelected</t>
+  </si>
+  <si>
     <t>Encounter.serviceType.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Encounter.priority</t>
@@ -1256,6 +1324,27 @@
     <t>ROL-3 (or maybe PRT-4)</t>
   </si>
   <si>
+    <t>Encounter.participant.type.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.type.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.type.coding</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://terminology.hl7.org/CodeSystem/v3-ParticipationType"/&gt;
+  &lt;code value="PPRF"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>1614-1: fixed value = http://terminology.hl7.org/CodeSystem/v3-ParticipationType#PPRF</t>
+  </si>
+  <si>
+    <t>Encounter.participant.type.text</t>
+  </si>
+  <si>
     <t>Encounter.participant.period</t>
   </si>
   <si>
@@ -1490,6 +1579,9 @@
     <t>Encounter.reasonCode.coding.system</t>
   </si>
   <si>
+    <t>447-1: undefined</t>
+  </si>
+  <si>
     <t>Encounter.reasonCode.coding.version</t>
   </si>
   <si>
@@ -1558,12 +1650,6 @@
   </si>
   <si>
     <t>Reason the encounter takes place, as specified using information from another resource. For admissions, this is the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
-  </si>
-  <si>
-    <t>452: reference from V POV - PROBLEM LIST ENTRY (9000010.07-.16)</t>
-  </si>
-  <si>
-    <t>Outpat.VDiagnosis.ProblemListIEN,Outpat.WorkloadVDiagnosis.ProblemListIEN</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -2287,7 +2373,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP108"/>
+  <dimension ref="A1:AP123"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.67578125" customWidth="true" bestFit="true"/>
@@ -4191,10 +4277,10 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>82</v>
@@ -4230,7 +4316,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4245,7 +4331,7 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>82</v>
@@ -4254,21 +4340,21 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4294,13 +4380,13 @@
         <v>156</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4314,7 +4400,7 @@
         <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -4350,7 +4436,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4365,30 +4451,30 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4411,13 +4497,13 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4468,7 +4554,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4492,21 +4578,21 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4529,16 +4615,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4588,7 +4674,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4612,21 +4698,21 @@
         <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4652,13 +4738,13 @@
         <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4687,10 +4773,10 @@
         <v>172</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4708,7 +4794,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>90</v>
@@ -4723,30 +4809,30 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4769,16 +4855,16 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4828,7 +4914,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4863,10 +4949,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4981,10 +5067,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5101,14 +5187,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5130,10 +5216,10 @@
         <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>139</v>
@@ -5188,7 +5274,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5223,10 +5309,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5252,10 +5338,10 @@
         <v>110</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5285,10 +5371,10 @@
         <v>172</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5306,7 +5392,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>90</v>
@@ -5341,10 +5427,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5367,13 +5453,13 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5424,7 +5510,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5459,10 +5545,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5485,13 +5571,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5522,7 +5608,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5540,7 +5626,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>90</v>
@@ -5555,30 +5641,30 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5601,13 +5687,13 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5658,7 +5744,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5693,10 +5779,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5811,10 +5897,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5931,14 +6017,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5960,10 +6046,10 @@
         <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>139</v>
@@ -6018,7 +6104,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6053,10 +6139,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6079,13 +6165,13 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6115,10 +6201,10 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -6136,7 +6222,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>90</v>
@@ -6171,10 +6257,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6197,13 +6283,13 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6254,7 +6340,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
@@ -6289,10 +6375,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6318,13 +6404,13 @@
         <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6353,10 +6439,10 @@
         <v>183</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6374,7 +6460,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6389,30 +6475,30 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6432,16 +6518,16 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>157</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>158</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6468,13 +6554,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6492,7 +6578,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>285</v>
+        <v>159</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6504,7 +6590,7 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6513,7 +6599,7 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>160</v>
@@ -6522,26 +6608,26 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6553,15 +6639,17 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6598,31 +6686,31 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6645,14 +6733,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6668,21 +6756,23 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>137</v>
+        <v>290</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>162</v>
+        <v>291</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6718,19 +6808,19 @@
         <v>82</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>166</v>
+        <v>294</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6742,7 +6832,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6754,21 +6844,21 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>160</v>
+        <v>295</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6779,7 +6869,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6788,23 +6878,19 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>295</v>
+        <v>157</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6852,19 +6938,19 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>299</v>
+        <v>159</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6876,32 +6962,32 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6913,15 +6999,17 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6958,31 +7046,31 @@
         <v>82</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -7005,44 +7093,46 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>137</v>
+        <v>300</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>162</v>
+        <v>301</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7051,7 +7141,7 @@
         <v>82</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>82</v>
@@ -7078,34 +7168,34 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>166</v>
+        <v>305</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
@@ -7114,21 +7204,21 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>160</v>
+        <v>307</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7151,20 +7241,18 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7212,7 +7300,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7236,21 +7324,21 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7264,7 +7352,7 @@
         <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7273,18 +7361,18 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7332,7 +7420,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7347,30 +7435,30 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7393,17 +7481,17 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7452,7 +7540,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7467,30 +7555,30 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7513,17 +7601,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>156</v>
+        <v>335</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7572,7 +7662,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7596,21 +7686,21 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7624,7 +7714,7 @@
         <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7633,19 +7723,19 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>336</v>
+        <v>156</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7694,7 +7784,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7709,30 +7799,30 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7755,20 +7845,16 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7792,13 +7878,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7816,7 +7902,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7837,24 +7923,24 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>350</v>
+        <v>160</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7877,13 +7963,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>353</v>
+        <v>157</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>354</v>
+        <v>158</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7910,13 +7996,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7934,7 +8020,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>352</v>
+        <v>159</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7946,7 +8032,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7958,53 +8044,53 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>356</v>
+        <v>160</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>360</v>
+        <v>135</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>361</v>
+        <v>136</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>362</v>
+        <v>137</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>363</v>
+        <v>162</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>364</v>
+        <v>139</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8042,57 +8128,57 @@
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>359</v>
+        <v>166</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>368</v>
+        <v>160</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8115,16 +8201,20 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>372</v>
+        <v>253</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>373</v>
+        <v>290</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8172,7 +8262,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>294</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8193,35 +8283,35 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>160</v>
+        <v>295</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>377</v>
+        <v>296</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8233,13 +8323,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>380</v>
+        <v>156</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>381</v>
+        <v>157</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>382</v>
+        <v>158</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8290,19 +8380,19 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>378</v>
+        <v>159</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8311,10 +8401,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>384</v>
+        <v>160</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8325,14 +8415,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8342,24 +8432,26 @@
         <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>235</v>
+        <v>136</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>386</v>
+        <v>137</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8396,19 +8488,19 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>385</v>
+        <v>166</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8420,7 +8512,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8429,24 +8521,24 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>389</v>
+        <v>160</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8460,25 +8552,29 @@
         <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>157</v>
+        <v>300</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8487,7 +8583,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>82</v>
@@ -8526,7 +8622,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>159</v>
+        <v>305</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8538,10 +8634,10 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
@@ -8550,32 +8646,32 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>160</v>
+        <v>307</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8584,19 +8680,19 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>137</v>
+        <v>310</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>162</v>
+        <v>311</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>139</v>
+        <v>312</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8646,19 +8742,19 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>166</v>
+        <v>313</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8670,56 +8766,54 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>160</v>
+        <v>314</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>243</v>
+        <v>317</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>145</v>
+        <v>319</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8768,45 +8862,45 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>245</v>
+        <v>320</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>133</v>
+        <v>323</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8817,10 +8911,10 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -8829,18 +8923,18 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>395</v>
+        <v>326</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8864,13 +8958,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8888,13 +8982,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>394</v>
+        <v>329</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8909,24 +9003,24 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>400</v>
+        <v>332</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>401</v>
+        <v>333</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8940,25 +9034,29 @@
         <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K56" t="s" s="2">
-        <v>208</v>
+        <v>335</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>403</v>
+        <v>336</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9006,7 +9104,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>402</v>
+        <v>340</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9021,7 +9119,7 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
@@ -9030,21 +9128,21 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>407</v>
+        <v>342</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>408</v>
+        <v>373</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>408</v>
+        <v>373</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9058,7 +9156,7 @@
         <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
@@ -9067,16 +9165,20 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>409</v>
+        <v>156</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>410</v>
+        <v>344</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9124,7 +9226,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>408</v>
+        <v>348</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9139,30 +9241,30 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>415</v>
+        <v>350</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>417</v>
+        <v>351</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>374</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>374</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9173,7 +9275,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9182,16 +9284,16 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>419</v>
+        <v>178</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>420</v>
+        <v>375</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>421</v>
+        <v>376</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9218,13 +9320,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9242,13 +9344,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>374</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9263,32 +9365,32 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>423</v>
+        <v>380</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>424</v>
+        <v>381</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>424</v>
+        <v>381</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
@@ -9300,19 +9402,19 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>208</v>
+        <v>383</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9362,7 +9464,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>424</v>
+        <v>381</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9377,30 +9479,30 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>429</v>
+        <v>390</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>430</v>
+        <v>391</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>431</v>
+        <v>392</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>432</v>
+        <v>393</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>432</v>
+        <v>393</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9411,7 +9513,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9420,16 +9522,16 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>156</v>
+        <v>394</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>157</v>
+        <v>395</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>158</v>
+        <v>396</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9480,19 +9582,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>159</v>
+        <v>393</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9501,28 +9603,28 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>160</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>135</v>
+        <v>401</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9541,17 +9643,15 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>136</v>
+        <v>402</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>137</v>
+        <v>403</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9588,19 +9688,19 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>166</v>
+        <v>400</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9612,7 +9712,7 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9621,10 +9721,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>160</v>
+        <v>406</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9635,10 +9735,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9649,7 +9749,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>91</v>
@@ -9661,17 +9761,15 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>435</v>
+        <v>237</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9720,45 +9818,45 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>443</v>
+        <v>411</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>444</v>
+        <v>412</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9772,33 +9870,29 @@
         <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>435</v>
+        <v>156</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>446</v>
+        <v>157</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q63" t="s" s="2">
-        <v>449</v>
-      </c>
+      <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9842,7 +9936,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>450</v>
+        <v>159</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9851,47 +9945,47 @@
         <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>452</v>
+        <v>160</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>414</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9903,16 +9997,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>455</v>
+        <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>456</v>
+        <v>137</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>457</v>
+        <v>162</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>458</v>
+        <v>139</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9962,19 +10056,19 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>454</v>
+        <v>166</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9983,28 +10077,28 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>459</v>
+        <v>160</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>460</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>461</v>
+        <v>415</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>461</v>
+        <v>415</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>462</v>
+        <v>244</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10014,27 +10108,29 @@
         <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>463</v>
+        <v>245</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>464</v>
+        <v>246</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10058,13 +10154,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10082,7 +10178,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>461</v>
+        <v>247</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10094,7 +10190,7 @@
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10103,24 +10199,24 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>469</v>
+        <v>133</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>472</v>
+        <v>416</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>472</v>
+        <v>416</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10131,27 +10227,29 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>157</v>
+        <v>417</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10176,13 +10274,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10200,19 +10298,19 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>159</v>
+        <v>416</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10221,35 +10319,35 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>160</v>
+        <v>422</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>473</v>
+        <v>424</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>473</v>
+        <v>424</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10261,17 +10359,15 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10308,31 +10404,31 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10355,14 +10451,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>474</v>
+        <v>425</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>474</v>
+        <v>425</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10378,23 +10474,21 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>251</v>
+        <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>295</v>
+        <v>137</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>296</v>
+        <v>162</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10430,19 +10524,19 @@
         <v>82</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>299</v>
+        <v>166</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10454,7 +10548,7 @@
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10466,21 +10560,21 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>475</v>
+        <v>426</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>475</v>
+        <v>426</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10491,28 +10585,32 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>156</v>
+        <v>253</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>157</v>
+        <v>290</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10521,7 +10619,7 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>82</v>
@@ -10560,22 +10658,22 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>159</v>
+        <v>294</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
@@ -10584,32 +10682,32 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>160</v>
+        <v>295</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>476</v>
+        <v>429</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>476</v>
+        <v>429</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10618,21 +10716,23 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>137</v>
+        <v>344</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>162</v>
+        <v>345</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10668,31 +10768,31 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>166</v>
+        <v>348</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10704,21 +10804,21 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>160</v>
+        <v>350</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>477</v>
+        <v>430</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>477</v>
+        <v>430</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10732,29 +10832,25 @@
         <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>104</v>
+        <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>305</v>
+        <v>431</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10802,7 +10898,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>309</v>
+        <v>430</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10817,7 +10913,7 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
@@ -10826,21 +10922,21 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>310</v>
+        <v>434</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>311</v>
+        <v>435</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>478</v>
+        <v>436</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>478</v>
+        <v>436</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10854,7 +10950,7 @@
         <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
@@ -10863,17 +10959,15 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>156</v>
+        <v>437</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>313</v>
+        <v>438</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10922,7 +11016,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>316</v>
+        <v>436</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10937,30 +11031,30 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>317</v>
+        <v>443</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>318</v>
+        <v>445</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10971,10 +11065,10 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
@@ -10983,18 +11077,16 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>110</v>
+        <v>447</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>320</v>
+        <v>448</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>321</v>
+        <v>449</v>
       </c>
       <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11042,13 +11134,13 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>323</v>
+        <v>446</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
@@ -11057,30 +11149,30 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>480</v>
+        <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>326</v>
+        <v>450</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>327</v>
+        <v>451</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11094,27 +11186,27 @@
         <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>329</v>
+        <v>453</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11162,7 +11254,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>332</v>
+        <v>452</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11183,24 +11275,24 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>333</v>
+        <v>457</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>334</v>
+        <v>459</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11220,23 +11312,19 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>336</v>
+        <v>156</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>337</v>
+        <v>157</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11284,7 +11372,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>341</v>
+        <v>159</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11296,7 +11384,7 @@
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11308,32 +11396,32 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>342</v>
+        <v>160</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11342,23 +11430,21 @@
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>345</v>
+        <v>137</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>346</v>
+        <v>162</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11394,31 +11480,31 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>349</v>
+        <v>166</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11430,32 +11516,32 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>350</v>
+        <v>160</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>462</v>
+        <v>82</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>91</v>
@@ -11467,16 +11553,16 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11526,45 +11612,45 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11575,10 +11661,10 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>82</v>
@@ -11587,20 +11673,24 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>235</v>
+        <v>463</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q78" s="2"/>
+      <c r="Q78" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="R78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11644,45 +11734,45 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11705,15 +11795,17 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>156</v>
+        <v>483</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>157</v>
+        <v>484</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11762,7 +11854,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11774,7 +11866,7 @@
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11783,28 +11875,28 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>160</v>
+        <v>487</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>135</v>
+        <v>490</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11814,25 +11906,25 @@
         <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>137</v>
+        <v>491</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>162</v>
+        <v>492</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>139</v>
+        <v>493</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11858,13 +11950,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -11882,7 +11974,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>166</v>
+        <v>489</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11894,7 +11986,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11903,60 +11995,56 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>160</v>
+        <v>497</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>243</v>
+        <v>157</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12004,19 +12092,19 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -12028,7 +12116,7 @@
         <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12039,42 +12127,42 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>496</v>
+        <v>135</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>497</v>
+        <v>136</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>498</v>
+        <v>137</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>499</v>
+        <v>162</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>465</v>
+        <v>139</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12112,57 +12200,57 @@
         <v>82</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>495</v>
+        <v>166</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>503</v>
+        <v>160</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12173,7 +12261,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12182,19 +12270,23 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>506</v>
+        <v>290</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12218,13 +12310,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12242,13 +12334,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>505</v>
+        <v>294</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12266,21 +12358,21 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>160</v>
+        <v>295</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12303,13 +12395,13 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>511</v>
+        <v>156</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>512</v>
+        <v>157</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>513</v>
+        <v>158</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12360,7 +12452,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>510</v>
+        <v>159</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12372,7 +12464,7 @@
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12384,7 +12476,7 @@
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>514</v>
+        <v>160</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12395,14 +12487,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12421,16 +12513,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>516</v>
+        <v>136</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>517</v>
+        <v>137</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>518</v>
+        <v>162</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>519</v>
+        <v>139</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12468,19 +12560,19 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>515</v>
+        <v>166</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12492,7 +12584,7 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12504,7 +12596,7 @@
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>520</v>
+        <v>160</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12515,10 +12607,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12538,21 +12630,23 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>522</v>
+        <v>300</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>523</v>
+        <v>301</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12600,7 +12694,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>521</v>
+        <v>305</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12615,7 +12709,7 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>82</v>
@@ -12624,21 +12718,21 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>525</v>
+        <v>307</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>526</v>
+        <v>507</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>526</v>
+        <v>507</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12658,18 +12752,20 @@
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>156</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>157</v>
+        <v>310</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12718,7 +12814,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>159</v>
+        <v>313</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12730,7 +12826,7 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12742,55 +12838,55 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>160</v>
+        <v>314</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>137</v>
+        <v>317</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12838,80 +12934,78 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>166</v>
+        <v>320</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>160</v>
+        <v>323</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>243</v>
+        <v>326</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>145</v>
+        <v>328</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12960,19 +13054,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>245</v>
+        <v>329</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12984,21 +13078,21 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>133</v>
+        <v>332</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13018,19 +13112,23 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>148</v>
+        <v>335</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>530</v>
+        <v>336</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13078,7 +13176,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>529</v>
+        <v>340</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13102,21 +13200,21 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>152</v>
+        <v>341</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>532</v>
+        <v>342</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13136,19 +13234,23 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>534</v>
+        <v>156</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>535</v>
+        <v>344</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13196,7 +13298,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>533</v>
+        <v>348</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13220,52 +13322,54 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>537</v>
+        <v>350</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>178</v>
+        <v>515</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>539</v>
+        <v>516</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13290,13 +13394,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>542</v>
+        <v>82</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13314,13 +13418,13 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
@@ -13335,24 +13439,24 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>543</v>
+        <v>497</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>544</v>
+        <v>499</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>545</v>
+        <v>517</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>545</v>
+        <v>517</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13363,7 +13467,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13372,16 +13476,16 @@
         <v>82</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>178</v>
+        <v>237</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>546</v>
+        <v>518</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>547</v>
+        <v>519</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13408,13 +13512,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13432,13 +13536,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>545</v>
+        <v>517</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13456,21 +13560,21 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>160</v>
+        <v>520</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>550</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>551</v>
+        <v>521</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>551</v>
+        <v>521</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13481,7 +13585,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13493,20 +13597,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>552</v>
+        <v>157</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>555</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13530,13 +13630,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>557</v>
+        <v>82</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13554,19 +13654,19 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>551</v>
+        <v>159</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -13578,25 +13678,25 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>558</v>
+        <v>160</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>559</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>560</v>
+        <v>522</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>560</v>
+        <v>522</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13615,15 +13715,17 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>561</v>
+        <v>137</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13648,13 +13750,13 @@
         <v>82</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>564</v>
+        <v>82</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13672,7 +13774,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>560</v>
+        <v>166</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13684,7 +13786,7 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -13696,25 +13798,25 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>565</v>
+        <v>160</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>567</v>
+        <v>523</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>567</v>
+        <v>523</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13727,22 +13829,26 @@
         <v>82</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>568</v>
+        <v>245</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -13766,13 +13872,13 @@
         <v>82</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>570</v>
+        <v>82</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13790,7 +13896,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>567</v>
+        <v>247</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13802,7 +13908,7 @@
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13814,29 +13920,29 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>572</v>
+        <v>133</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>573</v>
+        <v>82</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>574</v>
+        <v>524</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>574</v>
+        <v>524</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>90</v>
@@ -13848,18 +13954,20 @@
         <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>575</v>
+        <v>527</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13908,10 +14016,10 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>574</v>
+        <v>524</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>90</v>
@@ -13929,24 +14037,24 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>577</v>
+        <v>530</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>578</v>
+        <v>531</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>579</v>
+        <v>532</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>579</v>
+        <v>532</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13960,7 +14068,7 @@
         <v>90</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>82</v>
@@ -13972,10 +14080,10 @@
         <v>178</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>580</v>
+        <v>533</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>581</v>
+        <v>534</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14005,10 +14113,10 @@
         <v>114</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>582</v>
+        <v>535</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>583</v>
+        <v>536</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14026,7 +14134,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>579</v>
+        <v>532</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14050,21 +14158,21 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>584</v>
+        <v>160</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>585</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>586</v>
+        <v>537</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>586</v>
+        <v>537</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14075,10 +14183,10 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>82</v>
@@ -14087,17 +14195,15 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>235</v>
+        <v>538</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>587</v>
+        <v>539</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14146,13 +14252,13 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>586</v>
+        <v>537</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
@@ -14170,7 +14276,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>590</v>
+        <v>541</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14181,10 +14287,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>591</v>
+        <v>542</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>591</v>
+        <v>542</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14195,7 +14301,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14207,15 +14313,17 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>156</v>
+        <v>543</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>157</v>
+        <v>544</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14264,19 +14372,19 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>159</v>
+        <v>542</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14288,7 +14396,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>160</v>
+        <v>547</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14299,24 +14407,24 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>592</v>
+        <v>548</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>592</v>
+        <v>548</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>82</v>
@@ -14325,16 +14433,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>136</v>
+        <v>237</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>137</v>
+        <v>549</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>162</v>
+        <v>550</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>139</v>
+        <v>551</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14384,19 +14492,19 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>166</v>
+        <v>548</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14408,7 +14516,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>160</v>
+        <v>552</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14419,46 +14527,42 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>593</v>
+        <v>553</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>593</v>
+        <v>553</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>243</v>
+        <v>157</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14506,19 +14610,19 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
@@ -14530,7 +14634,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14541,24 +14645,24 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>594</v>
+        <v>554</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>594</v>
+        <v>554</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>82</v>
@@ -14567,15 +14671,17 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>595</v>
+        <v>136</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>596</v>
+        <v>137</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14624,79 +14730,81 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>594</v>
+        <v>166</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>598</v>
+        <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>600</v>
+        <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>415</v>
+        <v>160</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>601</v>
+        <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>602</v>
+        <v>82</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>603</v>
+        <v>555</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>603</v>
+        <v>555</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>604</v>
+        <v>245</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>605</v>
+        <v>246</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O104" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
       </c>
@@ -14720,13 +14828,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>608</v>
+        <v>82</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14744,19 +14852,19 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>603</v>
+        <v>247</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
@@ -14768,7 +14876,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>609</v>
+        <v>133</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14779,10 +14887,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>610</v>
+        <v>556</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>610</v>
+        <v>556</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14805,17 +14913,15 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>611</v>
+        <v>557</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -14840,13 +14946,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14864,7 +14970,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>610</v>
+        <v>556</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14888,21 +14994,21 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>82</v>
+        <v>559</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>616</v>
+        <v>560</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>616</v>
+        <v>560</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14925,13 +15031,13 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>208</v>
+        <v>561</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>617</v>
+        <v>562</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>618</v>
+        <v>563</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14982,7 +15088,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>616</v>
+        <v>560</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15006,7 +15112,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>406</v>
+        <v>564</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15017,10 +15123,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>619</v>
+        <v>565</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>619</v>
+        <v>565</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15034,7 +15140,7 @@
         <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>82</v>
@@ -15043,13 +15149,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>620</v>
+        <v>178</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>621</v>
+        <v>566</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>622</v>
+        <v>567</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15076,13 +15182,13 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>82</v>
+        <v>569</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15100,7 +15206,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>619</v>
+        <v>565</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15115,30 +15221,30 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>623</v>
+        <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>625</v>
+        <v>570</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>626</v>
+        <v>571</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>627</v>
+        <v>572</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>627</v>
+        <v>572</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15161,17 +15267,15 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>628</v>
+        <v>178</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>629</v>
+        <v>573</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>631</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15196,13 +15300,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>82</v>
+        <v>575</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>82</v>
+        <v>576</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15220,7 +15324,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>627</v>
+        <v>572</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15241,20 +15345,1808 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="AN108" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP108" t="s" s="2">
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP123" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP108">
+  <autoFilter ref="A1:AP123">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15264,7 +17156,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI107">
+  <conditionalFormatting sqref="A2:AI122">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4694" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4694" uniqueCount="662">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1579,7 +1579,10 @@
     <t>Encounter.reasonCode.coding.system</t>
   </si>
   <si>
-    <t>447-1: undefined</t>
+    <t>urn:see-termmap-in-mapParameter</t>
+  </si>
+  <si>
+    <t>447-1: fixed value = urn:see-termmap-in-mapParameter</t>
   </si>
   <si>
     <t>Encounter.reasonCode.coding.version</t>
@@ -12655,7 +12658,7 @@
         <v>82</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>82</v>
@@ -12709,7 +12712,7 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>82</v>
@@ -12729,10 +12732,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12849,10 +12852,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12949,10 +12952,10 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>82</v>
@@ -12969,10 +12972,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13089,10 +13092,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13211,10 +13214,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13333,10 +13336,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13359,10 +13362,10 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M92" t="s" s="2">
         <v>492</v>
@@ -13418,7 +13421,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13453,10 +13456,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13482,10 +13485,10 @@
         <v>237</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13536,7 +13539,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13560,7 +13563,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13571,10 +13574,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13689,10 +13692,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13809,10 +13812,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13931,14 +13934,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13957,13 +13960,13 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>493</v>
@@ -14016,7 +14019,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>90</v>
@@ -14037,24 +14040,24 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>498</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14080,10 +14083,10 @@
         <v>178</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14113,10 +14116,10 @@
         <v>114</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14134,7 +14137,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14169,10 +14172,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14195,13 +14198,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14252,7 +14255,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14276,7 +14279,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14287,10 +14290,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14313,16 +14316,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14372,7 +14375,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14396,7 +14399,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14407,10 +14410,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14436,13 +14439,13 @@
         <v>237</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14492,7 +14495,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14516,7 +14519,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14527,10 +14530,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14645,10 +14648,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14765,10 +14768,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14887,10 +14890,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14916,10 +14919,10 @@
         <v>148</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14970,7 +14973,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15000,15 +15003,15 @@
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15031,13 +15034,13 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15088,7 +15091,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15112,7 +15115,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15123,10 +15126,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15152,10 +15155,10 @@
         <v>178</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15185,10 +15188,10 @@
         <v>114</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15206,7 +15209,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15230,21 +15233,21 @@
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15270,10 +15273,10 @@
         <v>178</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15303,10 +15306,10 @@
         <v>355</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15324,7 +15327,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15354,15 +15357,15 @@
         <v>82</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15388,16 +15391,16 @@
         <v>178</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15425,10 +15428,10 @@
         <v>355</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15446,7 +15449,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15470,21 +15473,21 @@
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15510,10 +15513,10 @@
         <v>178</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15543,10 +15546,10 @@
         <v>114</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15564,7 +15567,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15588,21 +15591,21 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15628,10 +15631,10 @@
         <v>178</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15661,10 +15664,10 @@
         <v>114</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15682,7 +15685,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15706,21 +15709,21 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15743,13 +15746,13 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15800,7 +15803,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15824,21 +15827,21 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15864,10 +15867,10 @@
         <v>178</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15897,10 +15900,10 @@
         <v>114</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -15918,7 +15921,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15942,21 +15945,21 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15982,13 +15985,13 @@
         <v>237</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16038,7 +16041,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16062,7 +16065,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16073,10 +16076,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16191,10 +16194,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16311,10 +16314,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16433,10 +16436,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16459,13 +16462,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16516,7 +16519,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>90</v>
@@ -16531,30 +16534,30 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>443</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16580,13 +16583,13 @@
         <v>110</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16615,10 +16618,10 @@
         <v>172</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>82</v>
@@ -16636,7 +16639,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16660,7 +16663,7 @@
         <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -16671,10 +16674,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16700,13 +16703,13 @@
         <v>178</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16735,10 +16738,10 @@
         <v>355</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
@@ -16756,7 +16759,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16791,10 +16794,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16820,10 +16823,10 @@
         <v>210</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16874,7 +16877,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16909,10 +16912,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16935,13 +16938,13 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16992,7 +16995,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17007,30 +17010,30 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>442</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17053,16 +17056,16 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17112,7 +17115,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17133,10 +17136,10 @@
         <v>82</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,7 +617,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/terminology/VistADefinedTerms/9000010-15001</t>
+    <t>http://va.gov/fhir/identifiers/9000010-15001</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -626,7 +626,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>429-1: fixed value = http://va.gov/terminology/VistADefinedTerms/9000010-15001</t>
+    <t>429-1: fixed value = http://va.gov/fhir/identifiers/9000010-15001</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4694" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4693" uniqueCount="664">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,7 +617,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/9000010-15001</t>
+    <t>http://va.gov/identifiers/$Sta3n/9000010-15001</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -626,7 +626,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>429-1: fixed value = http://va.gov/fhir/identifiers/9000010-15001</t>
+    <t>429-1: fixed value = http://va.gov/identifiers/$Sta3n/9000010-15001</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>
@@ -1312,7 +1312,13 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFencounterParticipationType</t>
+  </si>
+  <si>
+    <t>1854: terminologyMaps using VF_encounterParticipationType on V PROVIDER - PRIMARY/SECONDARY (9000010.06-.04)</t>
+  </si>
+  <si>
+    <t>Outpat.VProvider.PrimarySecondary,Outpat.WorkloadVProvider.PrimarySecondary</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -2414,7 +2420,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="97.65625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="110.9921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="217.51953125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
@@ -10277,11 +10283,9 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
         <v>420</v>
       </c>
@@ -10316,30 +10320,30 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10454,10 +10458,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10574,10 +10578,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10622,7 +10626,7 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>82</v>
@@ -10676,7 +10680,7 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
@@ -10696,10 +10700,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10818,10 +10822,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10847,10 +10851,10 @@
         <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10901,7 +10905,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10916,7 +10920,7 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
@@ -10925,21 +10929,21 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10962,13 +10966,13 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11019,7 +11023,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11034,30 +11038,30 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11080,13 +11084,13 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11137,7 +11141,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11161,21 +11165,21 @@
         <v>405</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11201,13 +11205,13 @@
         <v>210</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11257,7 +11261,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11278,24 +11282,24 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11410,10 +11414,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11530,10 +11534,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11556,16 +11560,16 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11615,7 +11619,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11624,36 +11628,36 @@
         <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11676,23 +11680,23 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q78" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="R78" t="s" s="2">
         <v>82</v>
@@ -11737,7 +11741,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11746,13 +11750,13 @@
         <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>231</v>
@@ -11761,21 +11765,21 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11798,16 +11802,16 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11857,7 +11861,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11878,28 +11882,28 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11921,13 +11925,13 @@
         <v>178</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11956,10 +11960,10 @@
         <v>114</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -11977,7 +11981,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11998,24 +12002,24 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12130,10 +12134,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12250,10 +12254,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12372,10 +12376,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12490,10 +12494,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12610,10 +12614,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12658,7 +12662,7 @@
         <v>82</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>82</v>
@@ -12712,7 +12716,7 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>82</v>
@@ -12732,10 +12736,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12852,10 +12856,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12952,10 +12956,10 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>82</v>
@@ -12972,10 +12976,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13092,10 +13096,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13214,10 +13218,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13336,14 +13340,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13362,16 +13366,16 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13421,7 +13425,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13442,24 +13446,24 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13485,10 +13489,10 @@
         <v>237</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13539,7 +13543,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13563,7 +13567,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13574,10 +13578,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13692,10 +13696,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13812,10 +13816,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13934,14 +13938,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13960,16 +13964,16 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14019,7 +14023,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>90</v>
@@ -14040,24 +14044,24 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14083,10 +14087,10 @@
         <v>178</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14116,10 +14120,10 @@
         <v>114</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14137,7 +14141,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14172,10 +14176,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14198,13 +14202,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14255,7 +14259,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14279,7 +14283,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14290,10 +14294,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14316,16 +14320,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14375,7 +14379,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14399,7 +14403,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14410,10 +14414,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14439,13 +14443,13 @@
         <v>237</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14495,7 +14499,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14519,7 +14523,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14530,10 +14534,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14648,10 +14652,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14768,10 +14772,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14890,10 +14894,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14919,10 +14923,10 @@
         <v>148</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14973,7 +14977,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15003,15 +15007,15 @@
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15034,13 +15038,13 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15091,7 +15095,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15115,7 +15119,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15126,10 +15130,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15155,10 +15159,10 @@
         <v>178</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15188,10 +15192,10 @@
         <v>114</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15209,7 +15213,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15233,21 +15237,21 @@
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15273,10 +15277,10 @@
         <v>178</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15306,10 +15310,10 @@
         <v>355</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15327,7 +15331,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15357,15 +15361,15 @@
         <v>82</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15391,16 +15395,16 @@
         <v>178</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15428,10 +15432,10 @@
         <v>355</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15449,7 +15453,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15473,21 +15477,21 @@
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15513,10 +15517,10 @@
         <v>178</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15546,10 +15550,10 @@
         <v>114</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15567,7 +15571,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15591,21 +15595,21 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15631,10 +15635,10 @@
         <v>178</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15664,10 +15668,10 @@
         <v>114</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15685,7 +15689,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15709,21 +15713,21 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15746,13 +15750,13 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15803,7 +15807,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15827,21 +15831,21 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15867,10 +15871,10 @@
         <v>178</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15900,10 +15904,10 @@
         <v>114</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -15921,7 +15925,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15945,21 +15949,21 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15985,13 +15989,13 @@
         <v>237</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16041,7 +16045,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16065,7 +16069,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16076,10 +16080,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16194,10 +16198,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16314,10 +16318,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16436,10 +16440,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16462,13 +16466,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16519,7 +16523,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>90</v>
@@ -16534,30 +16538,30 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16583,13 +16587,13 @@
         <v>110</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16618,10 +16622,10 @@
         <v>172</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>82</v>
@@ -16639,7 +16643,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16663,7 +16667,7 @@
         <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -16674,10 +16678,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16703,13 +16707,13 @@
         <v>178</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16738,10 +16742,10 @@
         <v>355</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
@@ -16759,7 +16763,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16794,10 +16798,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16823,10 +16827,10 @@
         <v>210</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16877,7 +16881,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16901,7 +16905,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16912,10 +16916,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16938,13 +16942,13 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16995,7 +16999,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17010,30 +17014,30 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17056,16 +17060,16 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17115,7 +17119,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17136,10 +17140,10 @@
         <v>82</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$119</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4693" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4540" uniqueCount="658">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1328,27 +1328,6 @@
   </si>
   <si>
     <t>ROL-3 (or maybe PRT-4)</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://terminology.hl7.org/CodeSystem/v3-ParticipationType"/&gt;
-  &lt;code value="PPRF"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>1614-1: fixed value = http://terminology.hl7.org/CodeSystem/v3-ParticipationType#PPRF</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.text</t>
   </si>
   <si>
     <t>Encounter.participant.period</t>
@@ -2382,7 +2361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP123"/>
+  <dimension ref="A1:AP119"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.67578125" customWidth="true" bestFit="true"/>
@@ -10357,7 +10336,7 @@
         <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>82</v>
@@ -10366,13 +10345,13 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>157</v>
+        <v>427</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>158</v>
+        <v>428</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10423,7 +10402,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>159</v>
+        <v>426</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10435,10 +10414,10 @@
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>82</v>
@@ -10447,54 +10426,52 @@
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>160</v>
+        <v>430</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>136</v>
+        <v>433</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>137</v>
+        <v>434</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10531,57 +10508,57 @@
         <v>82</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>166</v>
+        <v>432</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>160</v>
+        <v>439</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10595,7 +10572,7 @@
         <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>82</v>
@@ -10604,20 +10581,16 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>253</v>
+        <v>443</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>290</v>
+        <v>444</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10626,7 +10599,7 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>82</v>
@@ -10665,7 +10638,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>294</v>
+        <v>442</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10680,30 +10653,30 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>295</v>
+        <v>446</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>296</v>
+        <v>447</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10717,29 +10690,27 @@
         <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>344</v>
+        <v>449</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>345</v>
+        <v>450</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10787,7 +10758,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>348</v>
+        <v>448</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10808,24 +10779,24 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>350</v>
+        <v>453</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>82</v>
+        <v>454</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>351</v>
+        <v>455</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10839,7 +10810,7 @@
         <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
@@ -10848,13 +10819,13 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>433</v>
+        <v>157</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>434</v>
+        <v>158</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10905,7 +10876,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>432</v>
+        <v>159</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10917,10 +10888,10 @@
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
@@ -10929,52 +10900,54 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>436</v>
+        <v>160</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>439</v>
+        <v>136</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>440</v>
+        <v>137</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11011,57 +10984,57 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>438</v>
+        <v>166</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>445</v>
+        <v>160</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11072,10 +11045,10 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
@@ -11084,15 +11057,17 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11141,45 +11116,45 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>453</v>
+        <v>468</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11199,25 +11174,27 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>210</v>
+        <v>459</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q74" s="2"/>
+      <c r="Q74" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="R74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11261,7 +11238,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11270,36 +11247,36 @@
         <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>460</v>
+        <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>461</v>
+        <v>477</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11322,15 +11299,17 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>156</v>
+        <v>479</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>157</v>
+        <v>480</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11379,7 +11358,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>159</v>
+        <v>478</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11391,7 +11370,7 @@
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11400,28 +11379,28 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>160</v>
+        <v>483</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>135</v>
+        <v>486</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11431,25 +11410,25 @@
         <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>137</v>
+        <v>487</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>162</v>
+        <v>488</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>139</v>
+        <v>489</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11475,31 +11454,31 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>166</v>
+        <v>485</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11511,7 +11490,7 @@
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11520,24 +11499,24 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>160</v>
+        <v>493</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11551,26 +11530,24 @@
         <v>90</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>465</v>
+        <v>156</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>466</v>
+        <v>157</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11619,7 +11596,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>469</v>
+        <v>159</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11628,76 +11605,74 @@
         <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>473</v>
+        <v>160</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>465</v>
+        <v>136</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>476</v>
+        <v>137</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>477</v>
+        <v>162</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>478</v>
+        <v>139</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q78" t="s" s="2">
-        <v>479</v>
-      </c>
+      <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11729,57 +11704,57 @@
         <v>82</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>480</v>
+        <v>166</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>482</v>
+        <v>160</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11790,7 +11765,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11799,21 +11774,23 @@
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>485</v>
+        <v>253</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>486</v>
+        <v>290</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>487</v>
+        <v>291</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11861,13 +11838,13 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>484</v>
+        <v>294</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
@@ -11882,57 +11859,55 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>489</v>
+        <v>295</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>490</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>493</v>
+        <v>157</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11957,13 +11932,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -11981,19 +11956,19 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>491</v>
+        <v>159</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12002,35 +11977,35 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>499</v>
+        <v>160</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12042,15 +12017,17 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12087,31 +12064,31 @@
         <v>82</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -12134,44 +12111,46 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>137</v>
+        <v>300</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>162</v>
+        <v>301</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12180,7 +12159,7 @@
         <v>82</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>82</v>
@@ -12207,34 +12186,34 @@
         <v>82</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>166</v>
+        <v>305</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>82</v>
@@ -12243,13 +12222,13 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>160</v>
+        <v>307</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -12268,7 +12247,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12280,20 +12259,18 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12341,13 +12318,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12365,13 +12342,13 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="84" hidden="true">
@@ -12393,25 +12370,27 @@
         <v>90</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>157</v>
+        <v>317</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>158</v>
+        <v>318</v>
       </c>
       <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12459,7 +12438,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>159</v>
+        <v>320</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12471,44 +12450,44 @@
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>160</v>
+        <v>323</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12517,21 +12496,21 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>137</v>
+        <v>326</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12567,31 +12546,31 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>166</v>
+        <v>329</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12603,21 +12582,21 @@
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>160</v>
+        <v>332</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12631,7 +12610,7 @@
         <v>90</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>82</v>
@@ -12640,19 +12619,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>104</v>
+        <v>335</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12662,7 +12641,7 @@
         <v>82</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>82</v>
@@ -12701,7 +12680,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>305</v>
+        <v>340</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12716,7 +12695,7 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>82</v>
@@ -12725,13 +12704,13 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>307</v>
+        <v>341</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>308</v>
+        <v>342</v>
       </c>
     </row>
     <row r="87" hidden="true">
@@ -12765,15 +12744,17 @@
         <v>156</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>310</v>
+        <v>344</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12821,7 +12802,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12845,13 +12826,13 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>315</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" hidden="true">
@@ -12863,14 +12844,14 @@
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>91</v>
@@ -12882,18 +12863,18 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>110</v>
+        <v>512</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>317</v>
+        <v>513</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12941,13 +12922,13 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>320</v>
+        <v>511</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
@@ -12956,22 +12937,22 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>512</v>
+        <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>323</v>
+        <v>493</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>324</v>
+        <v>495</v>
       </c>
     </row>
     <row r="89" hidden="true">
@@ -12990,7 +12971,7 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -13002,18 +12983,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>156</v>
+        <v>237</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>326</v>
+        <v>515</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>327</v>
+        <v>516</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>328</v>
-      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13061,13 +13040,13 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>329</v>
+        <v>514</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
@@ -13085,21 +13064,21 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>332</v>
+        <v>517</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13119,23 +13098,19 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>335</v>
+        <v>156</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>336</v>
+        <v>157</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13183,7 +13158,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>340</v>
+        <v>159</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13195,7 +13170,7 @@
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13207,32 +13182,32 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>341</v>
+        <v>160</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13241,23 +13216,21 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>344</v>
+        <v>137</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>345</v>
+        <v>162</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13305,19 +13278,19 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>348</v>
+        <v>166</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13329,25 +13302,25 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>350</v>
+        <v>160</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>492</v>
+        <v>244</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13357,27 +13330,29 @@
         <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I92" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>518</v>
+        <v>136</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>519</v>
+        <v>245</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>494</v>
+        <v>246</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13425,7 +13400,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>517</v>
+        <v>247</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13437,7 +13412,7 @@
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -13446,35 +13421,35 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>499</v>
+        <v>133</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13486,15 +13461,17 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>237</v>
+        <v>523</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13543,13 +13520,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13564,24 +13541,24 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13604,13 +13581,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>157</v>
+        <v>530</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>158</v>
+        <v>531</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13637,13 +13614,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13661,7 +13638,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>159</v>
+        <v>529</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13673,7 +13650,7 @@
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -13696,21 +13673,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13722,17 +13699,15 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>136</v>
+        <v>535</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>137</v>
+        <v>536</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13781,19 +13756,19 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>166</v>
+        <v>534</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -13805,7 +13780,7 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>160</v>
+        <v>538</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13816,14 +13791,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13836,26 +13811,24 @@
         <v>82</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>136</v>
+        <v>540</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>245</v>
+        <v>541</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>246</v>
+        <v>542</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -13903,7 +13876,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>247</v>
+        <v>539</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13915,7 +13888,7 @@
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13927,7 +13900,7 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>133</v>
+        <v>544</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13938,42 +13911,42 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>529</v>
+        <v>237</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>495</v>
+        <v>548</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14023,10 +13996,10 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>90</v>
@@ -14044,24 +14017,24 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14084,13 +14057,13 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>536</v>
+        <v>157</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>537</v>
+        <v>158</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14117,13 +14090,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>538</v>
+        <v>82</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14141,7 +14114,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>535</v>
+        <v>159</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14153,7 +14126,7 @@
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14176,21 +14149,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14202,15 +14175,17 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>541</v>
+        <v>136</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>542</v>
+        <v>137</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14259,19 +14234,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>540</v>
+        <v>166</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14283,7 +14258,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>544</v>
+        <v>160</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14294,14 +14269,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14314,24 +14289,26 @@
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>546</v>
+        <v>136</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>547</v>
+        <v>245</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>548</v>
+        <v>246</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14379,7 +14356,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>545</v>
+        <v>247</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14391,7 +14368,7 @@
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14403,7 +14380,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>550</v>
+        <v>133</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14414,10 +14391,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14431,7 +14408,7 @@
         <v>90</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>82</v>
@@ -14440,17 +14417,15 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>237</v>
+        <v>148</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14499,7 +14474,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14523,21 +14498,21 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>555</v>
+        <v>152</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>82</v>
+        <v>556</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14560,13 +14535,13 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>156</v>
+        <v>558</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>157</v>
+        <v>559</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>158</v>
+        <v>560</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14617,7 +14592,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>159</v>
+        <v>557</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14629,7 +14604,7 @@
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
@@ -14641,7 +14616,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>160</v>
+        <v>561</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14652,21 +14627,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -14678,17 +14653,15 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>137</v>
+        <v>563</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14713,13 +14686,13 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>82</v>
+        <v>565</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>82</v>
+        <v>566</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14737,19 +14710,19 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>166</v>
+        <v>562</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -14761,57 +14734,53 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>160</v>
+        <v>567</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>245</v>
+        <v>570</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>82</v>
       </c>
@@ -14835,13 +14804,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>82</v>
+        <v>572</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14859,19 +14828,19 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>247</v>
+        <v>569</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
@@ -14883,21 +14852,21 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>82</v>
+        <v>574</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14908,7 +14877,7 @@
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
@@ -14920,16 +14889,20 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -14953,13 +14926,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>82</v>
+        <v>580</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>82</v>
+        <v>581</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14977,13 +14950,13 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>82</v>
@@ -15001,21 +14974,21 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>152</v>
+        <v>582</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>562</v>
+        <v>583</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15026,7 +14999,7 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
@@ -15038,13 +15011,13 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>564</v>
+        <v>178</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15071,13 +15044,13 @@
         <v>82</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15095,13 +15068,13 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
@@ -15119,21 +15092,21 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>567</v>
+        <v>589</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>568</v>
+        <v>591</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>568</v>
+        <v>591</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15144,7 +15117,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>82</v>
@@ -15159,10 +15132,10 @@
         <v>178</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15192,10 +15165,10 @@
         <v>114</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15213,13 +15186,13 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>568</v>
+        <v>591</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
@@ -15237,21 +15210,21 @@
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>573</v>
+        <v>596</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>574</v>
+        <v>597</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>575</v>
+        <v>598</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>575</v>
+        <v>598</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15274,13 +15247,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>178</v>
+        <v>558</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>576</v>
+        <v>599</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>577</v>
+        <v>600</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15307,13 +15280,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15331,7 +15304,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>575</v>
+        <v>598</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15355,21 +15328,21 @@
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>160</v>
+        <v>601</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>580</v>
+        <v>602</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15380,10 +15353,10 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>82</v>
@@ -15395,17 +15368,13 @@
         <v>178</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15429,13 +15398,13 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>355</v>
+        <v>114</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15453,13 +15422,13 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>82</v>
@@ -15477,21 +15446,21 @@
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>589</v>
+        <v>609</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15505,7 +15474,7 @@
         <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>82</v>
@@ -15514,15 +15483,17 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>178</v>
+        <v>237</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15547,13 +15518,13 @@
         <v>82</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>593</v>
+        <v>82</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>594</v>
+        <v>82</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15571,7 +15542,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15595,21 +15566,21 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>595</v>
+        <v>614</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15620,7 +15591,7 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15632,13 +15603,13 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>598</v>
+        <v>157</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>599</v>
+        <v>158</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15665,13 +15636,13 @@
         <v>82</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>600</v>
+        <v>82</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>601</v>
+        <v>82</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15689,19 +15660,19 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>597</v>
+        <v>159</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>82</v>
@@ -15713,32 +15684,32 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>602</v>
+        <v>160</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>603</v>
+        <v>82</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>82</v>
@@ -15750,15 +15721,17 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>564</v>
+        <v>136</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>605</v>
+        <v>137</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15807,19 +15780,19 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>604</v>
+        <v>166</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
@@ -15831,53 +15804,57 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>607</v>
+        <v>160</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>608</v>
+        <v>82</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I113" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I113" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J113" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>610</v>
+        <v>245</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
       </c>
@@ -15901,13 +15878,13 @@
         <v>82</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>612</v>
+        <v>82</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>613</v>
+        <v>82</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -15925,19 +15902,19 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>609</v>
+        <v>247</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>82</v>
@@ -15949,21 +15926,21 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>614</v>
+        <v>133</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15971,10 +15948,10 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>91</v>
@@ -15986,17 +15963,15 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>237</v>
+        <v>619</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>619</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16045,13 +16020,13 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>82</v>
@@ -16060,30 +16035,30 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>82</v>
+        <v>622</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>82</v>
+        <v>623</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>82</v>
+        <v>624</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>620</v>
+        <v>439</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>82</v>
+        <v>626</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16106,15 +16081,17 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>157</v>
+        <v>628</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>629</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>630</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16139,13 +16116,13 @@
         <v>82</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>82</v>
+        <v>632</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>82</v>
@@ -16163,7 +16140,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>159</v>
+        <v>627</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16175,7 +16152,7 @@
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>82</v>
@@ -16187,7 +16164,7 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>160</v>
+        <v>633</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16198,21 +16175,21 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>82</v>
@@ -16224,16 +16201,16 @@
         <v>82</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>137</v>
+        <v>635</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>162</v>
+        <v>636</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>139</v>
+        <v>637</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16259,13 +16236,13 @@
         <v>82</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>82</v>
+        <v>638</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>82</v>
+        <v>639</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
@@ -16283,19 +16260,19 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>166</v>
+        <v>634</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>82</v>
@@ -16307,7 +16284,7 @@
         <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
@@ -16318,46 +16295,42 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>623</v>
+        <v>640</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>623</v>
+        <v>640</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>245</v>
+        <v>641</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16405,19 +16378,19 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>247</v>
+        <v>640</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>82</v>
@@ -16429,7 +16402,7 @@
         <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>133</v>
+        <v>430</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
@@ -16440,10 +16413,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>624</v>
+        <v>643</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>624</v>
+        <v>643</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16451,7 +16424,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>90</v>
@@ -16466,13 +16439,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>625</v>
+        <v>644</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>626</v>
+        <v>645</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>627</v>
+        <v>646</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16523,10 +16496,10 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>624</v>
+        <v>643</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>90</v>
@@ -16538,30 +16511,30 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>628</v>
+        <v>647</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>629</v>
+        <v>648</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>630</v>
+        <v>438</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>445</v>
+        <v>649</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>631</v>
+        <v>82</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>632</v>
+        <v>650</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16584,16 +16557,16 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>110</v>
+        <v>652</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>634</v>
+        <v>653</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>636</v>
+        <v>655</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16619,13 +16592,13 @@
         <v>82</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>638</v>
+        <v>82</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>82</v>
@@ -16643,7 +16616,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16664,496 +16637,20 @@
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>82</v>
+        <v>656</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>639</v>
+        <v>657</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP123" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP123">
+  <autoFilter ref="A1:AP119">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17163,7 +16660,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI122">
+  <conditionalFormatting sqref="A2:AI118">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1197,7 +1197,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -2001,7 +2001,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1210,7 +1210,7 @@
     <t>While the encounter is always about the patient, the patient might not actually be known in all contexts of use, and there may be a group of patients that could be anonymous (such as in a group therapy for Alcoholics Anonymous - where the recording of the encounter could be used for billing on the number of people/staff and not important to the context of the specific patients) or alternately in veterinary care a herd of sheep receiving treatment (where the animals are not individually tracked).</t>
   </si>
   <si>
-    <t>440: reference from VISIT - PATIENT NAME (9000010-.05)</t>
+    <t>440: reference from VISIT - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010-.05 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Outpat.Visit.PatientIEN,Outpat.Workload.PatientIEN</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1197,7 +1197,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>
@@ -1210,7 +1210,7 @@
     <t>While the encounter is always about the patient, the patient might not actually be known in all contexts of use, and there may be a group of patients that could be anonymous (such as in a group therapy for Alcoholics Anonymous - where the recording of the encounter could be used for billing on the number of people/staff and not important to the context of the specific patients) or alternately in veterinary care a herd of sheep receiving treatment (where the animals are not individually tracked).</t>
   </si>
   <si>
-    <t>440: reference from VISIT - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010-.05 &gt; 9000001-.01)</t>
+    <t>440: reference from VISIT - PATIENT NAME (9000010-.05)</t>
   </si>
   <si>
     <t>Outpat.Visit.PatientIEN,Outpat.Workload.PatientIEN</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1197,7 +1197,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4540" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4540" uniqueCount="661">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1717,6 +1717,9 @@
     <t>An Encounter may cover more than just the inpatient stay. Contexts such as outpatients, community clinics, and aged care facilities are also included.  The duration recorded in the period of this encounter covers the entire scope of this hospitalization record.</t>
+  </si>
+  <si>
+    <t>null: target not supported</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=ENC, moodCode=EVN]</t>
@@ -14017,7 +14020,7 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>82</v>
@@ -14026,7 +14029,7 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14037,10 +14040,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14155,10 +14158,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14275,10 +14278,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14397,10 +14400,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14426,10 +14429,10 @@
         <v>148</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14480,7 +14483,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14510,15 +14513,15 @@
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14541,13 +14544,13 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14598,7 +14601,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14622,7 +14625,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14633,10 +14636,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14662,10 +14665,10 @@
         <v>178</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14695,10 +14698,10 @@
         <v>114</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14716,7 +14719,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14740,21 +14743,21 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14780,10 +14783,10 @@
         <v>178</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14813,10 +14816,10 @@
         <v>355</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14834,7 +14837,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14864,15 +14867,15 @@
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14898,16 +14901,16 @@
         <v>178</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -14935,10 +14938,10 @@
         <v>355</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14956,7 +14959,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14980,21 +14983,21 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15020,10 +15023,10 @@
         <v>178</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15053,10 +15056,10 @@
         <v>114</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15074,7 +15077,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15098,21 +15101,21 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15138,10 +15141,10 @@
         <v>178</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15171,10 +15174,10 @@
         <v>114</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15192,7 +15195,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15216,21 +15219,21 @@
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15253,13 +15256,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15310,7 +15313,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15334,21 +15337,21 @@
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15374,10 +15377,10 @@
         <v>178</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15407,10 +15410,10 @@
         <v>114</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15428,7 +15431,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15452,21 +15455,21 @@
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15492,13 +15495,13 @@
         <v>237</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15548,7 +15551,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15572,7 +15575,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15583,10 +15586,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15701,10 +15704,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15821,10 +15824,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15943,10 +15946,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15969,13 +15972,13 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16026,7 +16029,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>90</v>
@@ -16041,30 +16044,30 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>439</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16090,13 +16093,13 @@
         <v>110</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16125,10 +16128,10 @@
         <v>172</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>82</v>
@@ -16146,7 +16149,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16170,7 +16173,7 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16181,10 +16184,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16210,13 +16213,13 @@
         <v>178</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16245,10 +16248,10 @@
         <v>355</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
@@ -16266,7 +16269,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16301,10 +16304,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16330,10 +16333,10 @@
         <v>210</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16384,7 +16387,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16419,10 +16422,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16445,13 +16448,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16502,7 +16505,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16517,30 +16520,30 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>438</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16563,16 +16566,16 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16622,7 +16625,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16643,10 +16646,10 @@
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1351,7 +1351,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1719,7 +1719,7 @@
 The duration recorded in the period of this encounter covers the entire scope of this hospitalization record.</t>
   </si>
   <si>
-    <t>null: target not supported</t>
+    <t>2030: target not supported</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=ENC, moodCode=EVN]</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$127</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4540" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4842" uniqueCount="672">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -812,7 +812,7 @@
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFencounterClass</t>
+    <t>http://va.gov/fhir/ValueSet/encounterClass</t>
   </si>
   <si>
     <t>614: terminologyMaps using VF_encounterClass on VISIT - PATIENT STATUS IN/OUT (9000010-15002)</t>
@@ -1312,7 +1312,7 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFencounterParticipationType</t>
+    <t>http://va.gov/fhir/ValueSet/encounterParticipationType</t>
   </si>
   <si>
     <t>1854: terminologyMaps using VF_encounterParticipationType on V PROVIDER - PRIMARY/SECONDARY (9000010.06-.04)</t>
@@ -1918,6 +1918,10 @@
     <t>Virtual encounters can be recorded in the Encounter by specifying a location reference to a location of type "kind" such as "client's home" and an encounter.class = "virtual".</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
     <t>.participation[typeCode=LOC]</t>
   </si>
   <si>
@@ -1931,80 +1935,111 @@
   </si>
   <si>
     <t>Encounter.location.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location)
+</t>
+  </si>
+  <si>
+    <t>Location the encounter takes place</t>
+  </si>
+  <si>
+    <t>The location where the encounter takes place.</t>
+  </si>
+  <si>
+    <t>Event.location</t>
+  </si>
+  <si>
+    <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>PV1-3 / PV1-6 / PV1-11 / PV1-42 / PV1-43</t>
+  </si>
+  <si>
+    <t>Encounter.location.status</t>
+  </si>
+  <si>
+    <t>planned | active | reserved | completed</t>
+  </si>
+  <si>
+    <t>The status of the participants' presence at the specified location during the period specified. If the participant is no longer at the location, then the period will have an end date/time.</t>
+  </si>
+  <si>
+    <t>When the patient is no longer active at a location, then the period end date is entered, and the status may be changed to completed.</t>
+  </si>
+  <si>
+    <t>The status of the location.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-location-status|4.0.1</t>
+  </si>
+  <si>
+    <t>.role.statusCode</t>
+  </si>
+  <si>
+    <t>Encounter.location.physicalType</t>
+  </si>
+  <si>
+    <t>The physical type of the location (usually the level in the location hierachy - bed room ward etc.)</t>
+  </si>
+  <si>
+    <t>This will be used to specify the required levels (bed/ward/room/etc.) desired to be recorded to simplify either messaging or query.</t>
+  </si>
+  <si>
+    <t>This information is de-normalized from the Location resource to support the easier understanding of the encounter resource and processing in messaging or query.
+There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
+  </si>
+  <si>
+    <t>Physical form of the location.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+  </si>
+  <si>
+    <t>Encounter.location.period</t>
+  </si>
+  <si>
+    <t>Time period during which the patient was present at the location</t>
+  </si>
+  <si>
+    <t>Time period during which the patient was present at the location.</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc</t>
+  </si>
+  <si>
+    <t>va-loc</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc.id</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc.extension</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc.location</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
   </si>
   <si>
-    <t>Location the encounter takes place</t>
-  </si>
-  <si>
-    <t>The location where the encounter takes place.</t>
-  </si>
-  <si>
-    <t>459: reference from VISIT - HOSPITAL LOCATION (9000010-.22) case location</t>
+    <t>459: reference from VISIT - HOSPITAL LOCATION (9000010-.22)</t>
   </si>
   <si>
     <t>Outpat.Visit.LocationIEN,Outpat.Workload.LocationIEN</t>
   </si>
   <si>
-    <t>Event.location</t>
-  </si>
-  <si>
-    <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>PV1-3 / PV1-6 / PV1-11 / PV1-42 / PV1-43</t>
-  </si>
-  <si>
-    <t>Encounter.location.status</t>
-  </si>
-  <si>
-    <t>planned | active | reserved | completed</t>
-  </si>
-  <si>
-    <t>The status of the participants' presence at the specified location during the period specified. If the participant is no longer at the location, then the period will have an end date/time.</t>
-  </si>
-  <si>
-    <t>When the patient is no longer active at a location, then the period end date is entered, and the status may be changed to completed.</t>
-  </si>
-  <si>
-    <t>The status of the location.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-location-status|4.0.1</t>
-  </si>
-  <si>
-    <t>.role.statusCode</t>
-  </si>
-  <si>
-    <t>Encounter.location.physicalType</t>
-  </si>
-  <si>
-    <t>The physical type of the location (usually the level in the location hierachy - bed room ward etc.)</t>
-  </si>
-  <si>
-    <t>This will be used to specify the required levels (bed/ward/room/etc.) desired to be recorded to simplify either messaging or query.</t>
-  </si>
-  <si>
-    <t>This information is de-normalized from the Location resource to support the easier understanding of the encounter resource and processing in messaging or query.
-There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
-  </si>
-  <si>
-    <t>Physical form of the location.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
-  </si>
-  <si>
-    <t>Encounter.location.period</t>
-  </si>
-  <si>
-    <t>Time period during which the patient was present at the location</t>
-  </si>
-  <si>
-    <t>Time period during which the patient was present at the location.</t>
+    <t>Encounter.location:va-loc.status</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc.physicalType</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc.period</t>
   </si>
   <si>
     <t>Encounter.serviceProvider</t>
@@ -2370,7 +2405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP119"/>
+  <dimension ref="A1:AP127"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.67578125" customWidth="true" bestFit="true"/>
@@ -15539,16 +15574,14 @@
         <v>82</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF110" t="s" s="2">
         <v>613</v>
@@ -15575,7 +15608,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15586,10 +15619,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15704,10 +15737,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15824,10 +15857,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15946,10 +15979,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15972,13 +16005,13 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16029,7 +16062,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>90</v>
@@ -16044,30 +16077,30 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
       <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>439</v>
       </c>
       <c r="AO114" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AP114" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>629</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16093,13 +16126,13 @@
         <v>110</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16128,11 +16161,11 @@
         <v>172</v>
       </c>
       <c r="Y115" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="Z115" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="Z115" t="s" s="2">
-        <v>635</v>
-      </c>
       <c r="AA115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16149,7 +16182,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16173,7 +16206,7 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16184,10 +16217,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16213,13 +16246,13 @@
         <v>178</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16248,11 +16281,11 @@
         <v>355</v>
       </c>
       <c r="Y116" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="Z116" t="s" s="2">
-        <v>642</v>
-      </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16269,7 +16302,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16304,10 +16337,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16333,10 +16366,10 @@
         <v>210</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16387,7 +16420,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16422,12 +16455,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C118" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="B118" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16448,15 +16483,17 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>647</v>
+        <v>237</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>648</v>
+        <v>614</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -16505,13 +16542,13 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>646</v>
+        <v>613</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>82</v>
@@ -16520,30 +16557,30 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>651</v>
+        <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>652</v>
+        <v>618</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>653</v>
+        <v>82</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>654</v>
+        <v>619</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16566,17 +16603,15 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>655</v>
+        <v>156</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>656</v>
+        <v>157</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>658</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -16625,41 +16660,997 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="AG119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
+      <c r="B123" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM119" t="s" s="2">
+      <c r="AK123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="AN119" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="AO119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP119" t="s" s="2">
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP127" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP119">
+  <autoFilter ref="A1:AP127">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16669,7 +17660,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI118">
+  <conditionalFormatting sqref="A2:AI126">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -557,7 +557,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-EncounterOutpatient-2035:if SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {null}EncounterOutpatient-2036:if Not SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {null}</t>
+eo-19-2035:409.68-.1 &gt; 409.1-.01: if SERVICE CONNECTED then http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {null}eo-19-2036:409.68-.1 &gt; 409.1-.01: if Not SERVICE CONNECTED then http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {null}</t>
   </si>
   <si>
     <t>2036: fixed value = http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" when OUTPATIENT ENCOUNTER - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (409.68-.1 &gt; 409.1-.01) case Not SERVICE CONNECTED</t>
@@ -817,7 +817,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-EncounterOutpatient-430:if null or &gt; now then fixed value #planned {null}EncounterOutpatient-431:if not null, &lt; now, .18 null then fixed value #in-progress {null}EncounterOutpatient-432:if not null, &lt; now then fixed value #finished {null}</t>
+eo-19-430:9000010-.01: if null or &gt; now then #planned {null}eo-19-431:9000010-.01: if not null, &lt; now, .18 null then #in-progress {null}eo-19-432:9000010-.18: if not null, &lt; now then #finished {null}</t>
   </si>
   <si>
     <t>432: fixed value = #finished when VISIT - CHECK OUT DATE&amp;TIME (9000010-.18) case not null, &lt; now</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$140</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5026" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5329" uniqueCount="710">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2089,6 +2089,39 @@
   </si>
   <si>
     <t>Time period during which the patient was present at the location.</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-stop</t>
+  </si>
+  <si>
+    <t>va-stop</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-stop.id</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-stop.extension</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-stop.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-stop.location</t>
+  </si>
+  <si>
+    <t>458: reference from VISIT - DSS ID (9000010-.08)</t>
+  </si>
+  <si>
+    <t>Outpat.Visit.PrimaryStopCodeIEN,Outpat.Visit.SecondaryStopCodeIEN,Outpat.Workload.PrimaryStopCodeIEN,Outpat.Workload.SecondaryStopCodeIEN</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-stop.status</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-stop.physicalType</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-stop.period</t>
   </si>
   <si>
     <t>Encounter.location:va-loc</t>
@@ -2491,7 +2524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP132"/>
+  <dimension ref="A1:AP140"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.75390625" customWidth="true" bestFit="true"/>
@@ -17637,7 +17670,7 @@
         <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>678</v>
+        <v>650</v>
       </c>
       <c r="L127" t="s" s="2">
         <v>651</v>
@@ -17709,10 +17742,10 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AL127" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>653</v>
@@ -17729,7 +17762,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>656</v>
@@ -17849,7 +17882,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>663</v>
@@ -17969,7 +18002,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>669</v>
@@ -18087,12 +18120,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C131" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="B131" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>82</v>
       </c>
@@ -18113,15 +18148,17 @@
         <v>82</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>685</v>
+        <v>265</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>686</v>
+        <v>641</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N131" s="2"/>
+        <v>642</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -18170,13 +18207,13 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>684</v>
+        <v>640</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>82</v>
@@ -18185,30 +18222,30 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>688</v>
+        <v>82</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>689</v>
+        <v>82</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>690</v>
+        <v>645</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>691</v>
+        <v>82</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>692</v>
+        <v>646</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18231,17 +18268,15 @@
         <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>693</v>
+        <v>149</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>694</v>
+        <v>150</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>696</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>82</v>
@@ -18290,41 +18325,997 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP132" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP133" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="P134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP134" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AP135" t="s" s="2">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="AG132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
+      <c r="B136" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM132" t="s" s="2">
+      <c r="AK136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP136" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP137" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP138" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="AN132" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="AO132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP132" t="s" s="2">
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP139" t="s" s="2">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AO140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP140" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP132">
+  <autoFilter ref="A1:AP140">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18334,7 +19325,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI131">
+  <conditionalFormatting sqref="A2:AI139">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5469" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5469" uniqueCount="723">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -748,6 +748,9 @@
     <t>Outpat.Visit.VisitIdentifier,Outpat.Workload.VisitIdentifier</t>
   </si>
   <si>
+    <t>Encounter.EncounterExtension.VisitID,Encounter.EncounterExtension.VisitID</t>
+  </si>
+  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
@@ -829,7 +832,7 @@
     <t>Outpat.Visit.CheckOutDateTime,Outpat.Workload.CheckOutDateTime</t>
   </si>
   <si>
-    <t>visit.dateTime,visit.visitString</t>
+    <t>Encounter.ToTime</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -913,9 +916,6 @@
     <t>Outpat.Visit.PatientStatusInOut,Outpat.Workload.PatientStatusInOut</t>
   </si>
   <si>
-    <t>visit.patientClass</t>
-  </si>
-  <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
   </si>
   <si>
@@ -989,6 +989,9 @@
   </si>
   <si>
     <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN</t>
+  </si>
+  <si>
+    <t>Encounter.EncounterExtension.Cpt,Encounter.EncounterExtension.Cpt,Procedure.Procedure,Procedure.CodeTableDetail.Procedure.Code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1255,7 +1258,7 @@
     <t>Outpat.Visit.ServiceCategory,Outpat.Workload.ServiceCategory</t>
   </si>
   <si>
-    <t>visit.serviceCategory,visit.visitString</t>
+    <t>Encounter.EncounterCodedType,Encounter.ExternalId,Encounter.ToTime</t>
   </si>
   <si>
     <t>Encounter.serviceType.coding.display</t>
@@ -1314,6 +1317,9 @@
     <t>Outpat.Visit.PatientIEN,Outpat.Workload.PatientIEN</t>
   </si>
   <si>
+    <t>Encounter.EncounterMRN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1465,6 +1471,9 @@
     <t>Outpat.VProvider.ProviderIEN,Outpat.WorkloadVProvider.ProviderIEN</t>
   </si>
   <si>
+    <t>Encounter.ConsultingClinicians</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1555,6 +1564,9 @@
     <t>Immun.ImmunizationContraRefusalEvent.VisitDateTime,Outpat.Visit.VisitDateTime,Outpat.VisitLogic.VisitDateTime,Outpat.Workload.VisitDateTime</t>
   </si>
   <si>
+    <t>Encounter.CareProvider.Description,Encounter.CareProvider.Name</t>
+  </si>
+  <si>
     <t>./low</t>
   </si>
   <si>
@@ -1681,6 +1693,9 @@
 Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
   </si>
   <si>
+    <t>Diagnosis.Diagnosis,Diagnosis.CodeTableDetail.Diagnosis.Code</t>
+  </si>
+  <si>
     <t>Encounter.reasonCode.coding.display</t>
   </si>
   <si>
@@ -1742,6 +1757,9 @@
   </si>
   <si>
     <t>Outpat.VDiagnosis.ProblemListIEN,Outpat.WorkloadVDiagnosis.ProblemListIEN</t>
+  </si>
+  <si>
+    <t>Diagnosis.DiagnosisExtension.ProblemId</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -2127,7 +2145,7 @@
     <t>Outpat.Visit.PrimaryStopCodeIEN,Outpat.Visit.SecondaryStopCodeIEN,Outpat.Workload.PrimaryStopCodeIEN,Outpat.Workload.SecondaryStopCodeIEN</t>
   </si>
   <si>
-    <t>visit.stopCode</t>
+    <t>Encounter.EncounterExtension.StopCode</t>
   </si>
   <si>
     <t>Encounter.location:va-stop.status</t>
@@ -2167,7 +2185,7 @@
     <t>Outpat.Visit.LocationIEN,Outpat.Workload.LocationIEN</t>
   </si>
   <si>
-    <t>visit.creditStopCode,visit.location,visit.service,visit.visitString</t>
+    <t>Encounter.ExternalId,Encounter.HealthCareFacility</t>
   </si>
   <si>
     <t>Encounter.location:va-loc.status</t>
@@ -2198,7 +2216,7 @@
     <t>Outpat.Visit.InstitutionIEN,Outpat.Workload.InstitutionIEN</t>
   </si>
   <si>
-    <t>visit.facility</t>
+    <t>Encounter.EncounterMRNAA,Encounter.EncounterNumberAssigningAuthority,Encounter.EnteredAt</t>
   </si>
   <si>
     <t>.particiaption[typeCode=PFM].role</t>
@@ -2585,7 +2603,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="217.19140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="217.51953125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="57.46875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="126.40625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -5281,27 +5299,27 @@
         <v>234</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>83</v>
+        <v>235</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5324,13 +5342,13 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5381,7 +5399,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5408,21 +5426,21 @@
         <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5445,16 +5463,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5504,7 +5522,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5531,21 +5549,21 @@
         <v>83</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5571,13 +5589,13 @@
         <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5606,10 +5624,10 @@
         <v>171</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -5627,7 +5645,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -5639,36 +5657,36 @@
         <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5691,16 +5709,16 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5750,7 +5768,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5788,10 +5806,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5909,10 +5927,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6032,14 +6050,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -6061,10 +6079,10 @@
         <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>181</v>
@@ -6119,7 +6137,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -6157,10 +6175,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6186,10 +6204,10 @@
         <v>111</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6219,10 +6237,10 @@
         <v>171</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -6240,7 +6258,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>91</v>
@@ -6278,10 +6296,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6304,13 +6322,13 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6361,7 +6379,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>91</v>
@@ -6399,10 +6417,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6428,10 +6446,10 @@
         <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6462,7 +6480,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>83</v>
@@ -6480,7 +6498,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>91</v>
@@ -6495,13 +6513,13 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>83</v>
@@ -6544,7 +6562,7 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>293</v>
@@ -6890,7 +6908,7 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6912,10 +6930,10 @@
         <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>181</v>
@@ -6970,7 +6988,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -7155,7 +7173,7 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>304</v>
@@ -7356,27 +7374,27 @@
         <v>313</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>290</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7494,10 +7512,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7617,10 +7635,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7646,16 +7664,16 @@
         <v>168</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7704,7 +7722,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7731,21 +7749,21 @@
         <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7863,10 +7881,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7986,10 +8004,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8015,16 +8033,16 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -8034,7 +8052,7 @@
         <v>83</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>83</v>
@@ -8073,7 +8091,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8088,7 +8106,7 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>83</v>
@@ -8100,21 +8118,21 @@
         <v>83</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8140,13 +8158,13 @@
         <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8196,7 +8214,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8223,21 +8241,21 @@
         <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8263,14 +8281,14 @@
         <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -8319,7 +8337,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8334,33 +8352,33 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8386,14 +8404,14 @@
         <v>150</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8442,7 +8460,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8457,33 +8475,33 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8506,19 +8524,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8567,7 +8585,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8594,21 +8612,21 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8634,16 +8652,16 @@
         <v>150</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8692,7 +8710,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8707,33 +8725,33 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8759,10 +8777,10 @@
         <v>206</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8789,13 +8807,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8813,7 +8831,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8837,7 +8855,7 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>154</v>
@@ -8846,15 +8864,15 @@
         <v>83</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8972,10 +8990,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9095,10 +9113,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9124,16 +9142,16 @@
         <v>168</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -9182,7 +9200,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9209,21 +9227,21 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9341,10 +9359,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9464,10 +9482,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9493,16 +9511,16 @@
         <v>105</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9512,7 +9530,7 @@
         <v>83</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>83</v>
@@ -9551,7 +9569,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9566,7 +9584,7 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
@@ -9578,21 +9596,21 @@
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9618,13 +9636,13 @@
         <v>150</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9674,7 +9692,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9701,21 +9719,21 @@
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9741,14 +9759,14 @@
         <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9797,7 +9815,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9812,33 +9830,33 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9864,14 +9882,14 @@
         <v>150</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9920,7 +9938,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9947,21 +9965,21 @@
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9984,19 +10002,19 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10045,7 +10063,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10072,21 +10090,21 @@
         <v>83</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10112,16 +10130,16 @@
         <v>150</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10170,7 +10188,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10197,21 +10215,21 @@
         <v>83</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10237,10 +10255,10 @@
         <v>206</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10267,13 +10285,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -10291,7 +10309,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10318,25 +10336,25 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10355,16 +10373,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10414,7 +10432,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10429,33 +10447,33 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>83</v>
+        <v>421</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10478,13 +10496,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10535,7 +10553,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10559,28 +10577,28 @@
         <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>154</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10599,13 +10617,13 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10656,7 +10674,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10680,10 +10698,10 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10694,10 +10712,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10720,13 +10738,13 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10777,7 +10795,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10801,24 +10819,24 @@
         <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10936,10 +10954,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11059,14 +11077,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -11088,10 +11106,10 @@
         <v>136</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>181</v>
@@ -11146,7 +11164,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11184,10 +11202,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11213,13 +11231,13 @@
         <v>206</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11249,7 +11267,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11267,7 +11285,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11282,33 +11300,33 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11331,13 +11349,13 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11388,7 +11406,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11403,7 +11421,7 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>83</v>
@@ -11415,21 +11433,21 @@
         <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11452,13 +11470,13 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11509,7 +11527,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11524,33 +11542,33 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>83</v>
+        <v>471</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11573,13 +11591,13 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11630,7 +11648,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11654,24 +11672,24 @@
         <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11694,16 +11712,16 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11753,7 +11771,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11777,24 +11795,24 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11912,10 +11930,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12035,10 +12053,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12061,16 +12079,16 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12120,7 +12138,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12129,39 +12147,39 @@
         <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>261</v>
+        <v>501</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12184,23 +12202,23 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q79" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="R79" t="s" s="2">
         <v>83</v>
@@ -12245,7 +12263,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12254,39 +12272,39 @@
         <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12309,16 +12327,16 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12368,7 +12386,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12392,28 +12410,28 @@
         <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12435,13 +12453,13 @@
         <v>206</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12470,10 +12488,10 @@
         <v>115</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12491,7 +12509,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12515,24 +12533,24 @@
         <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12650,10 +12668,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12773,10 +12791,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12802,16 +12820,16 @@
         <v>168</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12860,7 +12878,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12887,21 +12905,21 @@
         <v>83</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13019,10 +13037,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13142,10 +13160,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13171,16 +13189,16 @@
         <v>105</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -13190,7 +13208,7 @@
         <v>83</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>83</v>
@@ -13229,7 +13247,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13244,7 +13262,7 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>83</v>
@@ -13256,21 +13274,21 @@
         <v>83</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13296,13 +13314,13 @@
         <v>150</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13352,7 +13370,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13379,21 +13397,21 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13419,14 +13437,14 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13475,7 +13493,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13490,33 +13508,33 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>83</v>
+        <v>543</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13542,14 +13560,14 @@
         <v>150</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13598,7 +13616,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13625,21 +13643,21 @@
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13662,19 +13680,19 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13723,7 +13741,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13750,21 +13768,21 @@
         <v>83</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13790,16 +13808,16 @@
         <v>150</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13848,7 +13866,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13875,25 +13893,25 @@
         <v>83</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13912,16 +13930,16 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13971,7 +13989,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13995,24 +14013,24 @@
         <v>83</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14035,13 +14053,13 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14092,7 +14110,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14119,7 +14137,7 @@
         <v>83</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -14130,10 +14148,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14251,10 +14269,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14374,14 +14392,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14403,10 +14421,10 @@
         <v>136</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>181</v>
@@ -14461,7 +14479,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14499,14 +14517,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14525,16 +14543,16 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14584,7 +14602,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -14599,33 +14617,33 @@
         <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>83</v>
+        <v>564</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14651,10 +14669,10 @@
         <v>206</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14684,10 +14702,10 @@
         <v>115</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -14705,7 +14723,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14743,10 +14761,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14769,13 +14787,13 @@
         <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14826,7 +14844,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14853,7 +14871,7 @@
         <v>83</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -14864,10 +14882,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14890,16 +14908,16 @@
         <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14949,7 +14967,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14976,7 +14994,7 @@
         <v>83</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
@@ -14987,10 +15005,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15013,16 +15031,16 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -15072,7 +15090,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15087,7 +15105,7 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>83</v>
@@ -15099,7 +15117,7 @@
         <v>83</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
@@ -15110,10 +15128,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15231,10 +15249,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15354,14 +15372,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -15383,10 +15401,10 @@
         <v>136</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>181</v>
@@ -15441,7 +15459,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15479,10 +15497,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15508,10 +15526,10 @@
         <v>185</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15562,7 +15580,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15595,15 +15613,15 @@
         <v>83</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15626,13 +15644,13 @@
         <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15683,7 +15701,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15710,7 +15728,7 @@
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
@@ -15721,10 +15739,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15750,10 +15768,10 @@
         <v>206</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15783,10 +15801,10 @@
         <v>115</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -15804,7 +15822,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15831,21 +15849,21 @@
         <v>83</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15871,10 +15889,10 @@
         <v>206</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15901,13 +15919,13 @@
         <v>83</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>83</v>
@@ -15925,7 +15943,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15958,15 +15976,15 @@
         <v>83</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15992,16 +16010,16 @@
         <v>206</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -16026,31 +16044,31 @@
         <v>83</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="Z110" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16077,21 +16095,21 @@
         <v>83</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16117,10 +16135,10 @@
         <v>206</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16150,10 +16168,10 @@
         <v>115</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -16171,7 +16189,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16198,21 +16216,21 @@
         <v>83</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>624</v>
+        <v>630</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16238,10 +16256,10 @@
         <v>206</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16271,10 +16289,10 @@
         <v>115</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>83</v>
@@ -16292,7 +16310,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16319,21 +16337,21 @@
         <v>83</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16356,13 +16374,13 @@
         <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16413,7 +16431,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16440,21 +16458,21 @@
         <v>83</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>636</v>
+        <v>642</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16480,10 +16498,10 @@
         <v>206</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16513,10 +16531,10 @@
         <v>115</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -16534,7 +16552,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16561,21 +16579,21 @@
         <v>83</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ114" t="s" s="2">
-        <v>643</v>
+        <v>649</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16598,16 +16616,16 @@
         <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16645,7 +16663,7 @@
         <v>83</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="AC115" s="2"/>
       <c r="AD115" t="s" s="2">
@@ -16655,7 +16673,7 @@
         <v>140</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16682,7 +16700,7 @@
         <v>83</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>83</v>
@@ -16693,10 +16711,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16814,10 +16832,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16937,14 +16955,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16966,10 +16984,10 @@
         <v>136</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>181</v>
@@ -17024,7 +17042,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17062,10 +17080,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17088,13 +17106,13 @@
         <v>83</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17145,7 +17163,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>91</v>
@@ -17169,24 +17187,24 @@
         <v>83</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17212,13 +17230,13 @@
         <v>111</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17247,10 +17265,10 @@
         <v>171</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>83</v>
@@ -17268,7 +17286,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17295,7 +17313,7 @@
         <v>83</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>83</v>
@@ -17306,10 +17324,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17335,13 +17353,13 @@
         <v>206</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17367,13 +17385,13 @@
         <v>83</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>83</v>
@@ -17391,7 +17409,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17429,10 +17447,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17455,13 +17473,13 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17512,7 +17530,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17539,7 +17557,7 @@
         <v>83</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>83</v>
@@ -17550,13 +17568,13 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>83</v>
@@ -17578,16 +17596,16 @@
         <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17637,7 +17655,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17664,7 +17682,7 @@
         <v>83</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>83</v>
@@ -17675,10 +17693,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17796,10 +17814,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17919,14 +17937,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17948,10 +17966,10 @@
         <v>136</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>181</v>
@@ -18006,7 +18024,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18044,10 +18062,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18070,13 +18088,13 @@
         <v>83</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18127,7 +18145,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>91</v>
@@ -18142,33 +18160,33 @@
         <v>103</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18194,13 +18212,13 @@
         <v>111</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -18229,10 +18247,10 @@
         <v>171</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>83</v>
@@ -18250,7 +18268,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18277,7 +18295,7 @@
         <v>83</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>83</v>
@@ -18288,10 +18306,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18317,13 +18335,13 @@
         <v>206</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -18349,13 +18367,13 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -18373,7 +18391,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -18411,10 +18429,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18437,13 +18455,13 @@
         <v>83</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18494,7 +18512,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18521,7 +18539,7 @@
         <v>83</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AP130" t="s" s="2">
         <v>83</v>
@@ -18532,13 +18550,13 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>83</v>
@@ -18560,16 +18578,16 @@
         <v>83</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18619,7 +18637,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18646,7 +18664,7 @@
         <v>83</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>83</v>
@@ -18657,10 +18675,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18778,10 +18796,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18901,14 +18919,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18930,10 +18948,10 @@
         <v>136</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N134" t="s" s="2">
         <v>181</v>
@@ -18988,7 +19006,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -19026,10 +19044,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19052,13 +19070,13 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -19109,7 +19127,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>91</v>
@@ -19124,33 +19142,33 @@
         <v>103</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="AQ135" t="s" s="2">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19176,13 +19194,13 @@
         <v>111</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -19211,10 +19229,10 @@
         <v>171</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>83</v>
@@ -19232,7 +19250,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19259,7 +19277,7 @@
         <v>83</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>83</v>
@@ -19270,10 +19288,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19299,13 +19317,13 @@
         <v>206</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -19331,13 +19349,13 @@
         <v>83</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>83</v>
@@ -19355,7 +19373,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19393,10 +19411,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19419,13 +19437,13 @@
         <v>83</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19476,7 +19494,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19503,7 +19521,7 @@
         <v>83</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AP138" t="s" s="2">
         <v>83</v>
@@ -19514,10 +19532,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19540,13 +19558,13 @@
         <v>83</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19597,7 +19615,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19612,33 +19630,33 @@
         <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="AP139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>709</v>
+        <v>715</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19661,16 +19679,16 @@
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19720,7 +19738,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19744,10 +19762,10 @@
         <v>83</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -748,7 +748,7 @@
     <t>Outpat.Visit.VisitIdentifier,Outpat.Workload.VisitIdentifier</t>
   </si>
   <si>
-    <t>Encounter.EncounterExtension.VisitID,Encounter.EncounterExtension.VisitID</t>
+    <t>Encounter.Extension[EncounterExtension].VisitID,Encounter.Extension[EncounterExtension].VisitID</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -991,7 +991,7 @@
     <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN</t>
   </si>
   <si>
-    <t>Encounter.EncounterExtension.Cpt,Encounter.EncounterExtension.Cpt,Procedure.Procedure,Procedure.CodeTableDetail.Procedure.Code</t>
+    <t>Encounter.Extension[EncounterExtension].Cpt,Encounter.Extension[EncounterExtension].Cpt,Procedure.Procedure,Procedure.Procedure[CodeTableDetail.Procedure].Code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1564,7 +1564,7 @@
     <t>Immun.ImmunizationContraRefusalEvent.VisitDateTime,Outpat.Visit.VisitDateTime,Outpat.VisitLogic.VisitDateTime,Outpat.Workload.VisitDateTime</t>
   </si>
   <si>
-    <t>Encounter.CareProvider.Description,Encounter.CareProvider.Name</t>
+    <t>Encounter.ConsultingClinician[CareProvider].Description,Encounter.ConsultingClinician[CareProvider].Name</t>
   </si>
   <si>
     <t>./low</t>
@@ -1693,7 +1693,7 @@
 Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
   </si>
   <si>
-    <t>Diagnosis.Diagnosis,Diagnosis.CodeTableDetail.Diagnosis.Code</t>
+    <t>Diagnosis.Diagnosis,Diagnosis.Diagnosis[CodeTableDetail.Diagnosis].Code</t>
   </si>
   <si>
     <t>Encounter.reasonCode.coding.display</t>
@@ -1759,7 +1759,7 @@
     <t>Outpat.VDiagnosis.ProblemListIEN,Outpat.WorkloadVDiagnosis.ProblemListIEN</t>
   </si>
   <si>
-    <t>Diagnosis.DiagnosisExtension.ProblemId</t>
+    <t>Diagnosis.Extension[DiagnosisExtension].ProblemId</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -2145,7 +2145,7 @@
     <t>Outpat.Visit.PrimaryStopCodeIEN,Outpat.Visit.SecondaryStopCodeIEN,Outpat.Workload.PrimaryStopCodeIEN,Outpat.Workload.SecondaryStopCodeIEN</t>
   </si>
   <si>
-    <t>Encounter.EncounterExtension.StopCode</t>
+    <t>Encounter.Extension[EncounterExtension].StopCode</t>
   </si>
   <si>
     <t>Encounter.location:va-stop.status</t>
@@ -2603,7 +2603,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="217.19140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="217.51953125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="126.40625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="158.0234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file VISIT (9000010) to us-core-encounter</t>
+    <t>This StructureDefinition contains the maps for VistA file VISIT (9000010) to us-core-encounter.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5469" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5469" uniqueCount="724">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -553,7 +553,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/ResourceServiceConnection</t>
+    <t>http://va.gov/fhir/ValueSet/VSResourceServiceConnection</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1713,6 +1713,9 @@
   </si>
   <si>
     <t>Reason the encounter takes place (reference)</t>
+  </si>
+  <si>
+    <t>2152: target not supported</t>
   </si>
   <si>
     <t>Encounter.diagnosis</t>
@@ -2034,7 +2037,7 @@
     <t>Virtual encounters can be recorded in the Encounter by specifying a location reference to a location of type "kind" such as "client's home" and an encounter.class = "virtual".</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
@@ -2139,44 +2142,44 @@
     <t>Encounter.location:va-stop.location</t>
   </si>
   <si>
-    <t>458: reference from VISIT - DSS ID (9000010-.08)</t>
-  </si>
-  <si>
-    <t>Outpat.Visit.PrimaryStopCodeIEN,Outpat.Visit.SecondaryStopCodeIEN,Outpat.Workload.PrimaryStopCodeIEN,Outpat.Workload.SecondaryStopCodeIEN</t>
-  </si>
-  <si>
-    <t>Encounter.Extension[EncounterExtension].StopCode</t>
-  </si>
-  <si>
-    <t>Encounter.location:va-stop.status</t>
-  </si>
-  <si>
-    <t>Encounter.location:va-stop.physicalType</t>
-  </si>
-  <si>
-    <t>Encounter.location:va-stop.period</t>
-  </si>
-  <si>
-    <t>Encounter.location:va-loc</t>
-  </si>
-  <si>
-    <t>va-loc</t>
-  </si>
-  <si>
-    <t>Encounter.location:va-loc.id</t>
-  </si>
-  <si>
-    <t>Encounter.location:va-loc.extension</t>
-  </si>
-  <si>
-    <t>Encounter.location:va-loc.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.location:va-loc.location</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
+  </si>
+  <si>
+    <t>458: reference from VISIT - DSS ID (9000010-.08)</t>
+  </si>
+  <si>
+    <t>Outpat.Visit.PrimaryStopCodeIEN,Outpat.Visit.SecondaryStopCodeIEN,Outpat.Workload.PrimaryStopCodeIEN,Outpat.Workload.SecondaryStopCodeIEN</t>
+  </si>
+  <si>
+    <t>Encounter.Extension[EncounterExtension].StopCode</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-stop.status</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-stop.physicalType</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-stop.period</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc</t>
+  </si>
+  <si>
+    <t>va-loc</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc.id</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc.extension</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-loc.location</t>
   </si>
   <si>
     <t>459: reference from VISIT - HOSPITAL LOCATION (9000010-.22)</t>
@@ -14004,7 +14007,7 @@
         <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>83</v>
+        <v>550</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>83</v>
@@ -14027,10 +14030,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14056,10 +14059,10 @@
         <v>268</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14110,7 +14113,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14137,7 +14140,7 @@
         <v>83</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -14148,10 +14151,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14269,10 +14272,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14392,10 +14395,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14517,14 +14520,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14543,13 +14546,13 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>524</v>
@@ -14602,7 +14605,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -14617,33 +14620,33 @@
         <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>529</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14669,10 +14672,10 @@
         <v>206</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14702,10 +14705,10 @@
         <v>115</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -14723,7 +14726,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14761,10 +14764,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14787,13 +14790,13 @@
         <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14844,7 +14847,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14871,7 +14874,7 @@
         <v>83</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -14882,10 +14885,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14908,16 +14911,16 @@
         <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14967,7 +14970,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14994,7 +14997,7 @@
         <v>83</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
@@ -15005,10 +15008,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15034,13 +15037,13 @@
         <v>268</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -15090,7 +15093,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15105,7 +15108,7 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>83</v>
@@ -15117,7 +15120,7 @@
         <v>83</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
@@ -15128,10 +15131,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15249,10 +15252,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15372,10 +15375,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15497,10 +15500,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15526,10 +15529,10 @@
         <v>185</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15580,7 +15583,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15613,15 +15616,15 @@
         <v>83</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15644,13 +15647,13 @@
         <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15701,7 +15704,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15728,7 +15731,7 @@
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
@@ -15739,10 +15742,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15768,10 +15771,10 @@
         <v>206</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15801,10 +15804,10 @@
         <v>115</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -15822,7 +15825,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15849,21 +15852,21 @@
         <v>83</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15889,10 +15892,10 @@
         <v>206</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15922,10 +15925,10 @@
         <v>386</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>83</v>
@@ -15943,7 +15946,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15976,15 +15979,15 @@
         <v>83</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16010,16 +16013,16 @@
         <v>206</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -16047,10 +16050,10 @@
         <v>386</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>83</v>
@@ -16068,7 +16071,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16095,21 +16098,21 @@
         <v>83</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16135,10 +16138,10 @@
         <v>206</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16168,10 +16171,10 @@
         <v>115</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -16189,7 +16192,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16216,21 +16219,21 @@
         <v>83</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16256,10 +16259,10 @@
         <v>206</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16289,10 +16292,10 @@
         <v>115</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>83</v>
@@ -16310,7 +16313,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16337,21 +16340,21 @@
         <v>83</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16374,13 +16377,13 @@
         <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16431,7 +16434,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16458,21 +16461,21 @@
         <v>83</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16498,10 +16501,10 @@
         <v>206</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16531,10 +16534,10 @@
         <v>115</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -16552,7 +16555,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16579,21 +16582,21 @@
         <v>83</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ114" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16619,13 +16622,13 @@
         <v>268</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16663,7 +16666,7 @@
         <v>83</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AC115" s="2"/>
       <c r="AD115" t="s" s="2">
@@ -16673,7 +16676,7 @@
         <v>140</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16700,7 +16703,7 @@
         <v>83</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>83</v>
@@ -16711,10 +16714,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16832,10 +16835,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16955,10 +16958,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17080,10 +17083,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17106,13 +17109,13 @@
         <v>83</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17163,7 +17166,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>91</v>
@@ -17187,24 +17190,24 @@
         <v>83</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>473</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17230,13 +17233,13 @@
         <v>111</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17265,10 +17268,10 @@
         <v>171</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>83</v>
@@ -17286,7 +17289,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17313,7 +17316,7 @@
         <v>83</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>83</v>
@@ -17324,10 +17327,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17353,13 +17356,13 @@
         <v>206</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17388,10 +17391,10 @@
         <v>386</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>83</v>
@@ -17409,7 +17412,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17447,10 +17450,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17476,10 +17479,10 @@
         <v>239</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17530,7 +17533,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17568,13 +17571,13 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>83</v>
@@ -17599,13 +17602,13 @@
         <v>268</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17655,7 +17658,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17682,7 +17685,7 @@
         <v>83</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>83</v>
@@ -17693,10 +17696,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17814,10 +17817,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17937,10 +17940,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18062,10 +18065,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18088,13 +18091,13 @@
         <v>83</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>660</v>
+        <v>689</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18145,7 +18148,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>91</v>
@@ -18160,33 +18163,33 @@
         <v>103</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>473</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18212,13 +18215,13 @@
         <v>111</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -18247,10 +18250,10 @@
         <v>171</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>83</v>
@@ -18268,7 +18271,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18295,7 +18298,7 @@
         <v>83</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>83</v>
@@ -18306,10 +18309,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18335,13 +18338,13 @@
         <v>206</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -18370,10 +18373,10 @@
         <v>386</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -18391,7 +18394,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -18429,10 +18432,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18458,10 +18461,10 @@
         <v>239</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18512,7 +18515,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18550,13 +18553,13 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>83</v>
@@ -18581,13 +18584,13 @@
         <v>268</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18637,7 +18640,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18664,7 +18667,7 @@
         <v>83</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>83</v>
@@ -18675,10 +18678,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18796,10 +18799,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18919,10 +18922,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19044,10 +19047,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19070,13 +19073,13 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -19127,7 +19130,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>91</v>
@@ -19142,33 +19145,33 @@
         <v>103</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>473</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AQ135" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19194,13 +19197,13 @@
         <v>111</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -19229,10 +19232,10 @@
         <v>171</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>83</v>
@@ -19250,7 +19253,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19277,7 +19280,7 @@
         <v>83</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>83</v>
@@ -19288,10 +19291,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19317,13 +19320,13 @@
         <v>206</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -19352,10 +19355,10 @@
         <v>386</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>83</v>
@@ -19373,7 +19376,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19411,10 +19414,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19440,10 +19443,10 @@
         <v>239</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19494,7 +19497,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19532,10 +19535,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19558,13 +19561,13 @@
         <v>83</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19615,7 +19618,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19630,33 +19633,33 @@
         <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>472</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AP139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19679,16 +19682,16 @@
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19738,7 +19741,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19762,10 +19765,10 @@
         <v>83</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -560,10 +560,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-eo-19-2035:409.68-.1 &gt; 409.1-.01: if SERVICE CONNECTED then http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {null}eo-19-2036:409.68-.1 &gt; 409.1-.01: if Not SERVICE CONNECTED then http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {null}</t>
-  </si>
-  <si>
-    <t>2036: fixed value = http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" when OUTPATIENT ENCOUNTER - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (409.68-.1 &gt; 409.1-.01) case Not SERVICE CONNECTED</t>
+eo-19-2035:If (409.68-.1 &gt; 409.1-.01) is SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {null}eo-19-2036:If (409.68-.1 &gt; 409.1-.01) is Not SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {null}</t>
+  </si>
+  <si>
+    <t>2036: fixed value = http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" when OUTPATIENT ENCOUNTER - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (409.68-.1 &gt; 409.1-.01) if Not SERVICE CONNECTED</t>
   </si>
   <si>
     <t>Outpat.Visit.AppointmentTypeIEN,Outpat.Workload.AppointmentTypeIEN
@@ -742,7 +742,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>429: source value from VISIT - VISIT ID (9000010-15001)</t>
+    <t>429: source value based on VISIT - VISIT ID (9000010-15001)</t>
   </si>
   <si>
     <t>Outpat.Visit.VisitIdentifier,Outpat.Workload.VisitIdentifier</t>
@@ -823,10 +823,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-eo-19-430:9000010-.01: if null or &gt; now then #planned {null}eo-19-431:9000010-.01: if not null, &lt; now, .18 null then #in-progress {null}eo-19-432:9000010-.18: if not null, &lt; now then #finished {null}</t>
-  </si>
-  <si>
-    <t>432: fixed value = #finished when VISIT - CHECK OUT DATE&amp;TIME (9000010-.18) case not null, &lt; now</t>
+eo-19-430:If (9000010-.01) is null or &gt; now then fixed value #planned {null}eo-19-431:If (9000010-.01) is not null, &lt; now, .18 null then fixed value #in-progress {null}eo-19-432:If (9000010-.18) is not null, &lt; now then fixed value #finished {null}</t>
+  </si>
+  <si>
+    <t>432: fixed value = #finished when VISIT - CHECK OUT DATE&amp;TIME (9000010-.18) if not null, &lt; now</t>
   </si>
   <si>
     <t>Outpat.Visit.CheckOutDateTime,Outpat.Workload.CheckOutDateTime</t>
@@ -985,7 +985,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-encounter-type</t>
   </si>
   <si>
-    <t>1615: source value from V CPT - CPT &gt; CPT (9000010.18-.01 &gt; 81-)</t>
+    <t>1615: source value based on V CPT - CPT &gt; CPT (9000010.18-.01 &gt; 81-)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN</t>
@@ -1105,7 +1105,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1615-2: source value from V CPT - CPT &gt; CPT - CPT CODE (9000010.18-.01 &gt; 81-.01)</t>
+    <t>1615-2: source value based on V CPT - CPT &gt; CPT - CPT CODE (9000010.18-.01 &gt; 81-.01)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN
@@ -1133,7 +1133,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1615-3: source value from V CPT - CPT &gt; CPT - SHORT NAME (9000010.18-.01 &gt; 81-2)</t>
+    <t>1615-3: source value based on V CPT - CPT &gt; CPT - SHORT NAME (9000010.18-.01 &gt; 81-2)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN
@@ -1192,7 +1192,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1615-4: source value from V CPT - CPT &gt; CPT - SHORT NAME (9000010.18-.01 &gt; 81-2)</t>
+    <t>1615-4: source value based on V CPT - CPT &gt; CPT - SHORT NAME (9000010.18-.01 &gt; 81-2)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -1252,7 +1252,7 @@
     <t>Encounter.serviceType.coding.code</t>
   </si>
   <si>
-    <t>439: source value from VISIT - SERVICE CATEGORY (9000010-.07)</t>
+    <t>439: source value based on VISIT - SERVICE CATEGORY (9000010-.07)</t>
   </si>
   <si>
     <t>Outpat.Visit.ServiceCategory,Outpat.Workload.ServiceCategory</t>
@@ -1311,7 +1311,7 @@
     <t>While the encounter is always about the patient, the patient might not actually be known in all contexts of use, and there may be a group of patients that could be anonymous (such as in a group therapy for Alcoholics Anonymous - where the recording of the encounter could be used for billing on the number of people/staff and not important to the context of the specific patients) or alternately in veterinary care a herd of sheep receiving treatment (where the animals are not individually tracked).</t>
   </si>
   <si>
-    <t>440: reference from VISIT - PATIENT NAME (9000010-.05)</t>
+    <t>440: reference based on VISIT - PATIENT NAME (9000010-.05)</t>
   </si>
   <si>
     <t>Outpat.Visit.PatientIEN,Outpat.Workload.PatientIEN</t>
@@ -1465,7 +1465,7 @@
     <t>Persons involved in the encounter other than the patient.</t>
   </si>
   <si>
-    <t>1614: reference from V PROVIDER - PROVIDER &gt; NEW PERSON (9000010.06-.01 &gt; 200-)</t>
+    <t>1614: reference based on V PROVIDER - PROVIDER &gt; NEW PERSON (9000010.06-.01 &gt; 200-)</t>
   </si>
   <si>
     <t>Outpat.VProvider.ProviderIEN,Outpat.WorkloadVProvider.ProviderIEN</t>
@@ -1558,7 +1558,7 @@
 </t>
   </si>
   <si>
-    <t>443: source value from VISIT - VISIT/ADMIT DATE&amp;TIME (9000010-.01)</t>
+    <t>443: source value based on VISIT - VISIT/ADMIT DATE&amp;TIME (9000010-.01)</t>
   </si>
   <si>
     <t>Immun.ImmunizationContraRefusalEvent.VisitDateTime,Outpat.Visit.VisitDateTime,Outpat.VisitLogic.VisitDateTime,Outpat.Workload.VisitDateTime</t>
@@ -1591,7 +1591,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>444: source value from VISIT - CHECK OUT DATE&amp;TIME (9000010-.18)</t>
+    <t>444: source value based on VISIT - CHECK OUT DATE&amp;TIME (9000010-.18)</t>
   </si>
   <si>
     <t>./high</t>
@@ -1686,7 +1686,7 @@
     <t>Encounter.reasonCode.coding.code</t>
   </si>
   <si>
-    <t>447: source value from V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.07-.01 &gt; 80-.01)</t>
+    <t>447: source value based on V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.07-.01 &gt; 80-.01)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.ICDIEN,Outpat.WorkloadVDiagnosis.ICDIEN
@@ -1756,7 +1756,7 @@
     <t>Reason the encounter takes place, as specified using information from another resource. For admissions, this is the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
   </si>
   <si>
-    <t>452: reference from V POV - PROBLEM LIST ENTRY (9000010.07-.16)</t>
+    <t>452: reference based on V POV - PROBLEM LIST ENTRY (9000010.07-.16)</t>
   </si>
   <si>
     <t>Outpat.VDiagnosis.ProblemListIEN,Outpat.WorkloadVDiagnosis.ProblemListIEN</t>
@@ -2146,7 +2146,7 @@
 </t>
   </si>
   <si>
-    <t>458: reference from VISIT - DSS ID (9000010-.08)</t>
+    <t>458: reference based on VISIT - DSS ID (9000010-.08)</t>
   </si>
   <si>
     <t>Outpat.Visit.PrimaryStopCodeIEN,Outpat.Visit.SecondaryStopCodeIEN,Outpat.Workload.PrimaryStopCodeIEN,Outpat.Workload.SecondaryStopCodeIEN</t>
@@ -2182,7 +2182,7 @@
     <t>Encounter.location:va-loc.location</t>
   </si>
   <si>
-    <t>459: reference from VISIT - HOSPITAL LOCATION (9000010-.22)</t>
+    <t>459: reference based on VISIT - HOSPITAL LOCATION (9000010-.22)</t>
   </si>
   <si>
     <t>Outpat.Visit.LocationIEN,Outpat.Workload.LocationIEN</t>
@@ -2213,7 +2213,7 @@
     <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
   </si>
   <si>
-    <t>1599: reference from VISIT - LOC. OF ENCOUNTER &gt; LOCATION - NAME (9000010-.06 &gt; 9999999.06-.01)</t>
+    <t>1599: reference based on VISIT - LOC. OF ENCOUNTER &gt; LOCATION - NAME (9000010-.06 &gt; 9999999.06-.01)</t>
   </si>
   <si>
     <t>Outpat.Visit.InstitutionIEN,Outpat.Workload.InstitutionIEN</t>
@@ -2604,7 +2604,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="217.19140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="214.12890625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="217.51953125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="158.0234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5469" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5471" uniqueCount="726">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -907,6 +907,9 @@
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
+    <t>see mapping [VF_encounterClass](ConceptMap-VF-encounterClass.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/encounterClass</t>
   </si>
   <si>
@@ -1414,6 +1417,9 @@
   </si>
   <si>
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_encounterParticipationType](ConceptMap-VF-encounterParticipationType.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/encounterParticipationType</t>
@@ -6481,9 +6487,11 @@
       <c r="X32" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y32" s="2"/>
+      <c r="Y32" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>83</v>
@@ -6516,10 +6524,10 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>83</v>
@@ -6528,21 +6536,21 @@
         <v>83</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6568,10 +6576,10 @@
         <v>268</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6622,7 +6630,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6660,10 +6668,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6781,10 +6789,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6904,10 +6912,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7029,10 +7037,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7058,10 +7066,10 @@
         <v>168</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7091,10 +7099,10 @@
         <v>211</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -7112,7 +7120,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7150,10 +7158,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7179,10 +7187,10 @@
         <v>239</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7233,7 +7241,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -7271,10 +7279,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7300,13 +7308,13 @@
         <v>206</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7335,10 +7343,10 @@
         <v>211</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -7356,7 +7364,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7371,33 +7379,33 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7515,10 +7523,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7638,10 +7646,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7667,16 +7675,16 @@
         <v>168</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7725,7 +7733,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7752,21 +7760,21 @@
         <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7884,10 +7892,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8007,10 +8015,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8036,16 +8044,16 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -8055,7 +8063,7 @@
         <v>83</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>83</v>
@@ -8094,7 +8102,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8109,7 +8117,7 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>83</v>
@@ -8121,21 +8129,21 @@
         <v>83</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8161,13 +8169,13 @@
         <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8217,7 +8225,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8244,21 +8252,21 @@
         <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8284,14 +8292,14 @@
         <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -8340,7 +8348,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8355,33 +8363,33 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8407,14 +8415,14 @@
         <v>150</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8463,7 +8471,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8478,33 +8486,33 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8527,19 +8535,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8588,7 +8596,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8615,21 +8623,21 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8655,16 +8663,16 @@
         <v>150</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8713,7 +8721,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8728,33 +8736,33 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8780,10 +8788,10 @@
         <v>206</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8810,13 +8818,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8834,7 +8842,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8858,7 +8866,7 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>154</v>
@@ -8867,15 +8875,15 @@
         <v>83</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8993,10 +9001,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9116,10 +9124,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9145,16 +9153,16 @@
         <v>168</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -9203,7 +9211,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9230,21 +9238,21 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9362,10 +9370,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9485,10 +9493,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9514,16 +9522,16 @@
         <v>105</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9533,7 +9541,7 @@
         <v>83</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>83</v>
@@ -9572,7 +9580,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9587,7 +9595,7 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
@@ -9599,21 +9607,21 @@
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9639,13 +9647,13 @@
         <v>150</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9695,7 +9703,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9722,21 +9730,21 @@
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9762,14 +9770,14 @@
         <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9818,7 +9826,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9833,33 +9841,33 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9885,14 +9893,14 @@
         <v>150</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9941,7 +9949,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9968,21 +9976,21 @@
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10005,19 +10013,19 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10066,7 +10074,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10093,21 +10101,21 @@
         <v>83</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10133,16 +10141,16 @@
         <v>150</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10191,7 +10199,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10218,21 +10226,21 @@
         <v>83</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10258,10 +10266,10 @@
         <v>206</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10288,13 +10296,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -10312,7 +10320,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10339,25 +10347,25 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10376,16 +10384,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10435,7 +10443,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10450,33 +10458,33 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10499,13 +10507,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10556,7 +10564,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10580,28 +10588,28 @@
         <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>154</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10620,13 +10628,13 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10677,7 +10685,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10701,10 +10709,10 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10715,10 +10723,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10744,10 +10752,10 @@
         <v>268</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10798,7 +10806,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10822,24 +10830,24 @@
         <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10957,10 +10965,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11080,10 +11088,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11205,10 +11213,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11234,13 +11242,13 @@
         <v>206</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11268,9 +11276,11 @@
       <c r="X71" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y71" s="2"/>
+      <c r="Y71" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="Z71" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11288,7 +11298,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11303,33 +11313,33 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11355,10 +11365,10 @@
         <v>239</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11409,7 +11419,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11424,7 +11434,7 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>83</v>
@@ -11436,21 +11446,21 @@
         <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11473,13 +11483,13 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11530,7 +11540,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11545,33 +11555,33 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11594,13 +11604,13 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11651,7 +11661,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11675,24 +11685,24 @@
         <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11718,13 +11728,13 @@
         <v>239</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11774,7 +11784,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11798,24 +11808,24 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11933,10 +11943,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12056,10 +12066,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12082,16 +12092,16 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12141,7 +12151,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12150,39 +12160,39 @@
         <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12205,23 +12215,23 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q79" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="R79" t="s" s="2">
         <v>83</v>
@@ -12266,7 +12276,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12275,13 +12285,13 @@
         <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>261</v>
@@ -12293,21 +12303,21 @@
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12330,16 +12340,16 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12389,7 +12399,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12413,28 +12423,28 @@
         <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12456,13 +12466,13 @@
         <v>206</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12491,10 +12501,10 @@
         <v>115</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12512,7 +12522,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12536,24 +12546,24 @@
         <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12671,10 +12681,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12794,10 +12804,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12823,16 +12833,16 @@
         <v>168</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12881,7 +12891,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12908,21 +12918,21 @@
         <v>83</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13040,10 +13050,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13163,10 +13173,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13192,16 +13202,16 @@
         <v>105</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -13211,7 +13221,7 @@
         <v>83</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>83</v>
@@ -13250,7 +13260,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13265,7 +13275,7 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>83</v>
@@ -13277,21 +13287,21 @@
         <v>83</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13317,13 +13327,13 @@
         <v>150</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13373,7 +13383,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13400,21 +13410,21 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13440,14 +13450,14 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13496,7 +13506,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13511,33 +13521,33 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13563,14 +13573,14 @@
         <v>150</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13619,7 +13629,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13646,21 +13656,21 @@
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13683,19 +13693,19 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13744,7 +13754,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13771,21 +13781,21 @@
         <v>83</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13811,16 +13821,16 @@
         <v>150</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13869,7 +13879,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13896,25 +13906,25 @@
         <v>83</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13933,16 +13943,16 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13992,7 +14002,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14007,7 +14017,7 @@
         <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>83</v>
@@ -14016,24 +14026,24 @@
         <v>83</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14059,10 +14069,10 @@
         <v>268</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14113,7 +14123,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14140,7 +14150,7 @@
         <v>83</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -14151,10 +14161,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14272,10 +14282,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14395,10 +14405,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14520,14 +14530,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14546,16 +14556,16 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14605,7 +14615,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -14620,33 +14630,33 @@
         <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14672,10 +14682,10 @@
         <v>206</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14705,10 +14715,10 @@
         <v>115</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -14726,7 +14736,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14764,10 +14774,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14790,13 +14800,13 @@
         <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14847,7 +14857,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14874,7 +14884,7 @@
         <v>83</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -14885,10 +14895,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14911,16 +14921,16 @@
         <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14970,7 +14980,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14997,7 +15007,7 @@
         <v>83</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
@@ -15008,10 +15018,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15037,13 +15047,13 @@
         <v>268</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -15093,7 +15103,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15108,7 +15118,7 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>83</v>
@@ -15120,7 +15130,7 @@
         <v>83</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
@@ -15131,10 +15141,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15252,10 +15262,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15375,10 +15385,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15500,10 +15510,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15529,10 +15539,10 @@
         <v>185</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15583,7 +15593,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15616,15 +15626,15 @@
         <v>83</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15647,13 +15657,13 @@
         <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15704,7 +15714,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15731,7 +15741,7 @@
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
@@ -15742,10 +15752,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15771,10 +15781,10 @@
         <v>206</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15804,10 +15814,10 @@
         <v>115</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -15825,7 +15835,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15852,21 +15862,21 @@
         <v>83</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15892,10 +15902,10 @@
         <v>206</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15922,13 +15932,13 @@
         <v>83</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>83</v>
@@ -15946,7 +15956,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15979,15 +15989,15 @@
         <v>83</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16013,16 +16023,16 @@
         <v>206</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -16047,13 +16057,13 @@
         <v>83</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>83</v>
@@ -16071,7 +16081,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16098,21 +16108,21 @@
         <v>83</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16138,10 +16148,10 @@
         <v>206</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16171,10 +16181,10 @@
         <v>115</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -16192,7 +16202,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16219,21 +16229,21 @@
         <v>83</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16259,10 +16269,10 @@
         <v>206</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16292,10 +16302,10 @@
         <v>115</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>83</v>
@@ -16313,7 +16323,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16340,21 +16350,21 @@
         <v>83</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16377,13 +16387,13 @@
         <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16434,7 +16444,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16461,21 +16471,21 @@
         <v>83</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16501,10 +16511,10 @@
         <v>206</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16534,10 +16544,10 @@
         <v>115</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -16555,7 +16565,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16582,21 +16592,21 @@
         <v>83</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ114" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16622,13 +16632,13 @@
         <v>268</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16666,7 +16676,7 @@
         <v>83</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AC115" s="2"/>
       <c r="AD115" t="s" s="2">
@@ -16676,7 +16686,7 @@
         <v>140</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16703,7 +16713,7 @@
         <v>83</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>83</v>
@@ -16714,10 +16724,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16835,10 +16845,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16958,10 +16968,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17083,10 +17093,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17109,13 +17119,13 @@
         <v>83</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17166,7 +17176,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>91</v>
@@ -17190,24 +17200,24 @@
         <v>83</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17233,13 +17243,13 @@
         <v>111</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17268,10 +17278,10 @@
         <v>171</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>83</v>
@@ -17289,7 +17299,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17316,7 +17326,7 @@
         <v>83</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>83</v>
@@ -17327,10 +17337,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17356,13 +17366,13 @@
         <v>206</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17388,13 +17398,13 @@
         <v>83</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>83</v>
@@ -17412,7 +17422,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17450,10 +17460,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17479,10 +17489,10 @@
         <v>239</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17533,7 +17543,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17560,7 +17570,7 @@
         <v>83</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>83</v>
@@ -17571,13 +17581,13 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>83</v>
@@ -17602,13 +17612,13 @@
         <v>268</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17658,7 +17668,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17685,7 +17695,7 @@
         <v>83</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>83</v>
@@ -17696,10 +17706,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17817,10 +17827,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17940,10 +17950,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18065,10 +18075,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18091,13 +18101,13 @@
         <v>83</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18148,7 +18158,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>91</v>
@@ -18163,33 +18173,33 @@
         <v>103</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18215,13 +18225,13 @@
         <v>111</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -18250,10 +18260,10 @@
         <v>171</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>83</v>
@@ -18271,7 +18281,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18298,7 +18308,7 @@
         <v>83</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>83</v>
@@ -18309,10 +18319,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18338,13 +18348,13 @@
         <v>206</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -18370,13 +18380,13 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -18394,7 +18404,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -18432,10 +18442,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18461,10 +18471,10 @@
         <v>239</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18515,7 +18525,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18542,7 +18552,7 @@
         <v>83</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP130" t="s" s="2">
         <v>83</v>
@@ -18553,13 +18563,13 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>83</v>
@@ -18584,13 +18594,13 @@
         <v>268</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18640,7 +18650,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18667,7 +18677,7 @@
         <v>83</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>83</v>
@@ -18678,10 +18688,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18799,10 +18809,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18922,10 +18932,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19047,10 +19057,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19073,13 +19083,13 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -19130,7 +19140,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>91</v>
@@ -19145,33 +19155,33 @@
         <v>103</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AQ135" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19197,13 +19207,13 @@
         <v>111</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -19232,10 +19242,10 @@
         <v>171</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>83</v>
@@ -19253,7 +19263,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19280,7 +19290,7 @@
         <v>83</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>83</v>
@@ -19291,10 +19301,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19320,13 +19330,13 @@
         <v>206</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -19352,13 +19362,13 @@
         <v>83</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>83</v>
@@ -19376,7 +19386,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19414,10 +19424,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19443,10 +19453,10 @@
         <v>239</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19497,7 +19507,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19524,7 +19534,7 @@
         <v>83</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP138" t="s" s="2">
         <v>83</v>
@@ -19535,10 +19545,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19561,13 +19571,13 @@
         <v>83</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19618,7 +19628,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19633,33 +19643,33 @@
         <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AP139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19682,16 +19692,16 @@
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19741,7 +19751,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19765,10 +19775,10 @@
         <v>83</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -560,7 +560,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-eo-19-2035:If (409.68-.1 &gt; 409.1-.01) is SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {null}eo-19-2036:If (409.68-.1 &gt; 409.1-.01) is Not SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {null}</t>
+eo-19-2035:If (409.68-.1 &gt; 409.1-.01) is SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#SC "Service Connected" {true}eo-19-2036:If (409.68-.1 &gt; 409.1-.01) is Not SERVICE CONNECTED then fixed value http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" {true}</t>
   </si>
   <si>
     <t>2036: fixed value = http://va.gov/fhir/vistaDefinedTerms/409.1#NSC "Not Service Connected" when OUTPATIENT ENCOUNTER - APPOINTMENT TYPE &gt; APPOINTMENT TYPE - NAME (409.68-.1 &gt; 409.1-.01) if Not SERVICE CONNECTED</t>
@@ -823,7 +823,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-eo-19-430:If (9000010-.01) is null or &gt; now then fixed value #planned {null}eo-19-431:If (9000010-.01) is not null, &lt; now, .18 null then fixed value #in-progress {null}eo-19-432:If (9000010-.18) is not null, &lt; now then fixed value #finished {null}</t>
+eo-19-430:If (9000010-.01) is null or &gt; now then fixed value #planned {true}eo-19-431:If (9000010-.01) is not null, &lt; now, .18 null then fixed value #in-progress {true}eo-19-432:If (9000010-.18) is not null, &lt; now then fixed value #finished {true}</t>
   </si>
   <si>
     <t>432: fixed value = #finished when VISIT - CHECK OUT DATE&amp;TIME (9000010-.18) if not null, &lt; now</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1314,7 +1314,7 @@
     <t>While the encounter is always about the patient, the patient might not actually be known in all contexts of use, and there may be a group of patients that could be anonymous (such as in a group therapy for Alcoholics Anonymous - where the recording of the encounter could be used for billing on the number of people/staff and not important to the context of the specific patients) or alternately in veterinary care a herd of sheep receiving treatment (where the animals are not individually tracked).</t>
   </si>
   <si>
-    <t>440: reference based on VISIT - PATIENT NAME (9000010-.05)</t>
+    <t>440: reference based on VISIT - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010-.05 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Outpat.Visit.PatientIEN,Outpat.Workload.PatientIEN</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatient.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
